--- a/modelos/modelo_importacao_servidores.xlsx
+++ b/modelos/modelo_importacao_servidores.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores" sheetId="1" r:id="R5a93a6751b21451a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruções" sheetId="2" r:id="R6a42fa12fc1941d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="3" r:id="Re7532a526ca54670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores" sheetId="1" r:id="R6266639fbbf8423a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruções" sheetId="2" r:id="R8de470d7537c41f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="3" r:id="Rc7884af7c946431f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="66">
+  <x:cellXfs count="67">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -352,6 +352,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -516,6 +517,7 @@
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="35" customHeight="1">
@@ -543,6 +545,9 @@
       <x:c r="H1" s="6" t="str">
         <x:v>Carga Horária Mensal</x:v>
       </x:c>
+      <x:c r="I1" s="59" t="str">
+        <x:v>Lei Larissa (Sim/Não)</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
@@ -568,6 +573,9 @@
         <x:f>IF(D2=40,200,IF(D2=30,150,""))</x:f>
         <x:v>200</x:v>
       </x:c>
+      <x:c r="I2" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="17" t="str">
@@ -594,6 +602,9 @@
       <x:c r="H3" s="43" t="n">
         <x:f>IF(D3=40,200,IF(D3=30,150,""))</x:f>
         <x:v>150</x:v>
+      </x:c>
+      <x:c r="I3" s="59" t="str">
+        <x:v>Não</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -607,6 +618,9 @@
       <x:c r="H4" s="43" t="str">
         <x:f>IF(D4=40,200,IF(D4=30,150,""))</x:f>
       </x:c>
+      <x:c r="I4" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="17"/>
@@ -619,6 +633,9 @@
       <x:c r="H5" s="43" t="str">
         <x:f>IF(D5=40,200,IF(D5=30,150,""))</x:f>
       </x:c>
+      <x:c r="I5" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="17"/>
@@ -631,6 +648,9 @@
       <x:c r="H6" s="43" t="str">
         <x:f>IF(D6=40,200,IF(D6=30,150,""))</x:f>
       </x:c>
+      <x:c r="I6" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17"/>
@@ -643,6 +663,9 @@
       <x:c r="H7" s="43" t="str">
         <x:f>IF(D7=40,200,IF(D7=30,150,""))</x:f>
       </x:c>
+      <x:c r="I7" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17"/>
@@ -655,6 +678,9 @@
       <x:c r="H8" s="43" t="str">
         <x:f>IF(D8=40,200,IF(D8=30,150,""))</x:f>
       </x:c>
+      <x:c r="I8" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17"/>
@@ -667,6 +693,9 @@
       <x:c r="H9" s="43" t="str">
         <x:f>IF(D9=40,200,IF(D9=30,150,""))</x:f>
       </x:c>
+      <x:c r="I9" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17"/>
@@ -679,6 +708,9 @@
       <x:c r="H10" s="43" t="str">
         <x:f>IF(D10=40,200,IF(D10=30,150,""))</x:f>
       </x:c>
+      <x:c r="I10" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17"/>
@@ -691,6 +723,9 @@
       <x:c r="H11" s="43" t="str">
         <x:f>IF(D11=40,200,IF(D11=30,150,""))</x:f>
       </x:c>
+      <x:c r="I11" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17"/>
@@ -703,6 +738,9 @@
       <x:c r="H12" s="43" t="str">
         <x:f>IF(D12=40,200,IF(D12=30,150,""))</x:f>
       </x:c>
+      <x:c r="I12" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17"/>
@@ -715,6 +753,9 @@
       <x:c r="H13" s="43" t="str">
         <x:f>IF(D13=40,200,IF(D13=30,150,""))</x:f>
       </x:c>
+      <x:c r="I13" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17"/>
@@ -727,6 +768,9 @@
       <x:c r="H14" s="43" t="str">
         <x:f>IF(D14=40,200,IF(D14=30,150,""))</x:f>
       </x:c>
+      <x:c r="I14" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17"/>
@@ -739,6 +783,9 @@
       <x:c r="H15" s="43" t="str">
         <x:f>IF(D15=40,200,IF(D15=30,150,""))</x:f>
       </x:c>
+      <x:c r="I15" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17"/>
@@ -751,6 +798,9 @@
       <x:c r="H16" s="43" t="str">
         <x:f>IF(D16=40,200,IF(D16=30,150,""))</x:f>
       </x:c>
+      <x:c r="I16" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17"/>
@@ -763,6 +813,9 @@
       <x:c r="H17" s="43" t="str">
         <x:f>IF(D17=40,200,IF(D17=30,150,""))</x:f>
       </x:c>
+      <x:c r="I17" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17"/>
@@ -775,6 +828,9 @@
       <x:c r="H18" s="43" t="str">
         <x:f>IF(D18=40,200,IF(D18=30,150,""))</x:f>
       </x:c>
+      <x:c r="I18" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="17"/>
@@ -787,6 +843,9 @@
       <x:c r="H19" s="43" t="str">
         <x:f>IF(D19=40,200,IF(D19=30,150,""))</x:f>
       </x:c>
+      <x:c r="I19" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="17"/>
@@ -799,6 +858,9 @@
       <x:c r="H20" s="43" t="str">
         <x:f>IF(D20=40,200,IF(D20=30,150,""))</x:f>
       </x:c>
+      <x:c r="I20" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="17"/>
@@ -811,6 +873,9 @@
       <x:c r="H21" s="43" t="str">
         <x:f>IF(D21=40,200,IF(D21=30,150,""))</x:f>
       </x:c>
+      <x:c r="I21" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="17"/>
@@ -823,6 +888,9 @@
       <x:c r="H22" s="43" t="str">
         <x:f>IF(D22=40,200,IF(D22=30,150,""))</x:f>
       </x:c>
+      <x:c r="I22" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="17"/>
@@ -835,6 +903,9 @@
       <x:c r="H23" s="43" t="str">
         <x:f>IF(D23=40,200,IF(D23=30,150,""))</x:f>
       </x:c>
+      <x:c r="I23" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="17"/>
@@ -847,6 +918,9 @@
       <x:c r="H24" s="43" t="str">
         <x:f>IF(D24=40,200,IF(D24=30,150,""))</x:f>
       </x:c>
+      <x:c r="I24" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="17"/>
@@ -859,6 +933,9 @@
       <x:c r="H25" s="43" t="str">
         <x:f>IF(D25=40,200,IF(D25=30,150,""))</x:f>
       </x:c>
+      <x:c r="I25" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="17"/>
@@ -871,6 +948,9 @@
       <x:c r="H26" s="43" t="str">
         <x:f>IF(D26=40,200,IF(D26=30,150,""))</x:f>
       </x:c>
+      <x:c r="I26" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="17"/>
@@ -883,6 +963,9 @@
       <x:c r="H27" s="43" t="str">
         <x:f>IF(D27=40,200,IF(D27=30,150,""))</x:f>
       </x:c>
+      <x:c r="I27" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="17"/>
@@ -895,6 +978,9 @@
       <x:c r="H28" s="43" t="str">
         <x:f>IF(D28=40,200,IF(D28=30,150,""))</x:f>
       </x:c>
+      <x:c r="I28" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="17"/>
@@ -907,6 +993,9 @@
       <x:c r="H29" s="43" t="str">
         <x:f>IF(D29=40,200,IF(D29=30,150,""))</x:f>
       </x:c>
+      <x:c r="I29" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="17"/>
@@ -919,6 +1008,9 @@
       <x:c r="H30" s="43" t="str">
         <x:f>IF(D30=40,200,IF(D30=30,150,""))</x:f>
       </x:c>
+      <x:c r="I30" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="17"/>
@@ -931,6 +1023,9 @@
       <x:c r="H31" s="43" t="str">
         <x:f>IF(D31=40,200,IF(D31=30,150,""))</x:f>
       </x:c>
+      <x:c r="I31" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="17"/>
@@ -943,6 +1038,9 @@
       <x:c r="H32" s="43" t="str">
         <x:f>IF(D32=40,200,IF(D32=30,150,""))</x:f>
       </x:c>
+      <x:c r="I32" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="17"/>
@@ -955,6 +1053,9 @@
       <x:c r="H33" s="43" t="str">
         <x:f>IF(D33=40,200,IF(D33=30,150,""))</x:f>
       </x:c>
+      <x:c r="I33" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="17"/>
@@ -967,6 +1068,9 @@
       <x:c r="H34" s="43" t="str">
         <x:f>IF(D34=40,200,IF(D34=30,150,""))</x:f>
       </x:c>
+      <x:c r="I34" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="17"/>
@@ -979,6 +1083,9 @@
       <x:c r="H35" s="43" t="str">
         <x:f>IF(D35=40,200,IF(D35=30,150,""))</x:f>
       </x:c>
+      <x:c r="I35" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="17"/>
@@ -991,6 +1098,9 @@
       <x:c r="H36" s="43" t="str">
         <x:f>IF(D36=40,200,IF(D36=30,150,""))</x:f>
       </x:c>
+      <x:c r="I36" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="17"/>
@@ -1003,6 +1113,9 @@
       <x:c r="H37" s="43" t="str">
         <x:f>IF(D37=40,200,IF(D37=30,150,""))</x:f>
       </x:c>
+      <x:c r="I37" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="17"/>
@@ -1015,6 +1128,9 @@
       <x:c r="H38" s="43" t="str">
         <x:f>IF(D38=40,200,IF(D38=30,150,""))</x:f>
       </x:c>
+      <x:c r="I38" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="17"/>
@@ -1027,6 +1143,9 @@
       <x:c r="H39" s="43" t="str">
         <x:f>IF(D39=40,200,IF(D39=30,150,""))</x:f>
       </x:c>
+      <x:c r="I39" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="17"/>
@@ -1039,6 +1158,9 @@
       <x:c r="H40" s="43" t="str">
         <x:f>IF(D40=40,200,IF(D40=30,150,""))</x:f>
       </x:c>
+      <x:c r="I40" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="17"/>
@@ -1051,6 +1173,9 @@
       <x:c r="H41" s="43" t="str">
         <x:f>IF(D41=40,200,IF(D41=30,150,""))</x:f>
       </x:c>
+      <x:c r="I41" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="17"/>
@@ -1063,6 +1188,9 @@
       <x:c r="H42" s="43" t="str">
         <x:f>IF(D42=40,200,IF(D42=30,150,""))</x:f>
       </x:c>
+      <x:c r="I42" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="17"/>
@@ -1075,6 +1203,9 @@
       <x:c r="H43" s="43" t="str">
         <x:f>IF(D43=40,200,IF(D43=30,150,""))</x:f>
       </x:c>
+      <x:c r="I43" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="17"/>
@@ -1087,6 +1218,9 @@
       <x:c r="H44" s="43" t="str">
         <x:f>IF(D44=40,200,IF(D44=30,150,""))</x:f>
       </x:c>
+      <x:c r="I44" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="17"/>
@@ -1099,6 +1233,9 @@
       <x:c r="H45" s="43" t="str">
         <x:f>IF(D45=40,200,IF(D45=30,150,""))</x:f>
       </x:c>
+      <x:c r="I45" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="17"/>
@@ -1111,6 +1248,9 @@
       <x:c r="H46" s="43" t="str">
         <x:f>IF(D46=40,200,IF(D46=30,150,""))</x:f>
       </x:c>
+      <x:c r="I46" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="17"/>
@@ -1123,6 +1263,9 @@
       <x:c r="H47" s="43" t="str">
         <x:f>IF(D47=40,200,IF(D47=30,150,""))</x:f>
       </x:c>
+      <x:c r="I47" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="17"/>
@@ -1135,6 +1278,9 @@
       <x:c r="H48" s="43" t="str">
         <x:f>IF(D48=40,200,IF(D48=30,150,""))</x:f>
       </x:c>
+      <x:c r="I48" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="17"/>
@@ -1147,6 +1293,9 @@
       <x:c r="H49" s="43" t="str">
         <x:f>IF(D49=40,200,IF(D49=30,150,""))</x:f>
       </x:c>
+      <x:c r="I49" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="17"/>
@@ -1159,6 +1308,9 @@
       <x:c r="H50" s="43" t="str">
         <x:f>IF(D50=40,200,IF(D50=30,150,""))</x:f>
       </x:c>
+      <x:c r="I50" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="17"/>
@@ -1171,6 +1323,9 @@
       <x:c r="H51" s="43" t="str">
         <x:f>IF(D51=40,200,IF(D51=30,150,""))</x:f>
       </x:c>
+      <x:c r="I51" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="17"/>
@@ -1183,6 +1338,9 @@
       <x:c r="H52" s="43" t="str">
         <x:f>IF(D52=40,200,IF(D52=30,150,""))</x:f>
       </x:c>
+      <x:c r="I52" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="17"/>
@@ -1195,6 +1353,9 @@
       <x:c r="H53" s="43" t="str">
         <x:f>IF(D53=40,200,IF(D53=30,150,""))</x:f>
       </x:c>
+      <x:c r="I53" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="17"/>
@@ -1207,6 +1368,9 @@
       <x:c r="H54" s="43" t="str">
         <x:f>IF(D54=40,200,IF(D54=30,150,""))</x:f>
       </x:c>
+      <x:c r="I54" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="17"/>
@@ -1219,6 +1383,9 @@
       <x:c r="H55" s="43" t="str">
         <x:f>IF(D55=40,200,IF(D55=30,150,""))</x:f>
       </x:c>
+      <x:c r="I55" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="17"/>
@@ -1231,6 +1398,9 @@
       <x:c r="H56" s="43" t="str">
         <x:f>IF(D56=40,200,IF(D56=30,150,""))</x:f>
       </x:c>
+      <x:c r="I56" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="17"/>
@@ -1243,6 +1413,9 @@
       <x:c r="H57" s="43" t="str">
         <x:f>IF(D57=40,200,IF(D57=30,150,""))</x:f>
       </x:c>
+      <x:c r="I57" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="17"/>
@@ -1255,6 +1428,9 @@
       <x:c r="H58" s="43" t="str">
         <x:f>IF(D58=40,200,IF(D58=30,150,""))</x:f>
       </x:c>
+      <x:c r="I58" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="17"/>
@@ -1267,6 +1443,9 @@
       <x:c r="H59" s="43" t="str">
         <x:f>IF(D59=40,200,IF(D59=30,150,""))</x:f>
       </x:c>
+      <x:c r="I59" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="17"/>
@@ -1279,6 +1458,9 @@
       <x:c r="H60" s="43" t="str">
         <x:f>IF(D60=40,200,IF(D60=30,150,""))</x:f>
       </x:c>
+      <x:c r="I60" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="17"/>
@@ -1291,6 +1473,9 @@
       <x:c r="H61" s="43" t="str">
         <x:f>IF(D61=40,200,IF(D61=30,150,""))</x:f>
       </x:c>
+      <x:c r="I61" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="17"/>
@@ -1303,6 +1488,9 @@
       <x:c r="H62" s="43" t="str">
         <x:f>IF(D62=40,200,IF(D62=30,150,""))</x:f>
       </x:c>
+      <x:c r="I62" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="17"/>
@@ -1315,6 +1503,9 @@
       <x:c r="H63" s="43" t="str">
         <x:f>IF(D63=40,200,IF(D63=30,150,""))</x:f>
       </x:c>
+      <x:c r="I63" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="17"/>
@@ -1327,6 +1518,9 @@
       <x:c r="H64" s="43" t="str">
         <x:f>IF(D64=40,200,IF(D64=30,150,""))</x:f>
       </x:c>
+      <x:c r="I64" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="17"/>
@@ -1339,6 +1533,9 @@
       <x:c r="H65" s="43" t="str">
         <x:f>IF(D65=40,200,IF(D65=30,150,""))</x:f>
       </x:c>
+      <x:c r="I65" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="17"/>
@@ -1351,6 +1548,9 @@
       <x:c r="H66" s="43" t="str">
         <x:f>IF(D66=40,200,IF(D66=30,150,""))</x:f>
       </x:c>
+      <x:c r="I66" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="17"/>
@@ -1363,6 +1563,9 @@
       <x:c r="H67" s="43" t="str">
         <x:f>IF(D67=40,200,IF(D67=30,150,""))</x:f>
       </x:c>
+      <x:c r="I67" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="17"/>
@@ -1375,6 +1578,9 @@
       <x:c r="H68" s="43" t="str">
         <x:f>IF(D68=40,200,IF(D68=30,150,""))</x:f>
       </x:c>
+      <x:c r="I68" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="17"/>
@@ -1387,6 +1593,9 @@
       <x:c r="H69" s="43" t="str">
         <x:f>IF(D69=40,200,IF(D69=30,150,""))</x:f>
       </x:c>
+      <x:c r="I69" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="17"/>
@@ -1399,6 +1608,9 @@
       <x:c r="H70" s="43" t="str">
         <x:f>IF(D70=40,200,IF(D70=30,150,""))</x:f>
       </x:c>
+      <x:c r="I70" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="17"/>
@@ -1411,6 +1623,9 @@
       <x:c r="H71" s="43" t="str">
         <x:f>IF(D71=40,200,IF(D71=30,150,""))</x:f>
       </x:c>
+      <x:c r="I71" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="17"/>
@@ -1423,6 +1638,9 @@
       <x:c r="H72" s="43" t="str">
         <x:f>IF(D72=40,200,IF(D72=30,150,""))</x:f>
       </x:c>
+      <x:c r="I72" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="17"/>
@@ -1435,6 +1653,9 @@
       <x:c r="H73" s="43" t="str">
         <x:f>IF(D73=40,200,IF(D73=30,150,""))</x:f>
       </x:c>
+      <x:c r="I73" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="17"/>
@@ -1447,6 +1668,9 @@
       <x:c r="H74" s="43" t="str">
         <x:f>IF(D74=40,200,IF(D74=30,150,""))</x:f>
       </x:c>
+      <x:c r="I74" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="17"/>
@@ -1459,6 +1683,9 @@
       <x:c r="H75" s="43" t="str">
         <x:f>IF(D75=40,200,IF(D75=30,150,""))</x:f>
       </x:c>
+      <x:c r="I75" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="17"/>
@@ -1471,6 +1698,9 @@
       <x:c r="H76" s="43" t="str">
         <x:f>IF(D76=40,200,IF(D76=30,150,""))</x:f>
       </x:c>
+      <x:c r="I76" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="17"/>
@@ -1483,6 +1713,9 @@
       <x:c r="H77" s="43" t="str">
         <x:f>IF(D77=40,200,IF(D77=30,150,""))</x:f>
       </x:c>
+      <x:c r="I77" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="17"/>
@@ -1495,6 +1728,9 @@
       <x:c r="H78" s="43" t="str">
         <x:f>IF(D78=40,200,IF(D78=30,150,""))</x:f>
       </x:c>
+      <x:c r="I78" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="17"/>
@@ -1507,6 +1743,9 @@
       <x:c r="H79" s="43" t="str">
         <x:f>IF(D79=40,200,IF(D79=30,150,""))</x:f>
       </x:c>
+      <x:c r="I79" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="17"/>
@@ -1519,6 +1758,9 @@
       <x:c r="H80" s="43" t="str">
         <x:f>IF(D80=40,200,IF(D80=30,150,""))</x:f>
       </x:c>
+      <x:c r="I80" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="17"/>
@@ -1531,6 +1773,9 @@
       <x:c r="H81" s="43" t="str">
         <x:f>IF(D81=40,200,IF(D81=30,150,""))</x:f>
       </x:c>
+      <x:c r="I81" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="17"/>
@@ -1543,6 +1788,9 @@
       <x:c r="H82" s="43" t="str">
         <x:f>IF(D82=40,200,IF(D82=30,150,""))</x:f>
       </x:c>
+      <x:c r="I82" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="17"/>
@@ -1555,6 +1803,9 @@
       <x:c r="H83" s="43" t="str">
         <x:f>IF(D83=40,200,IF(D83=30,150,""))</x:f>
       </x:c>
+      <x:c r="I83" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="17"/>
@@ -1567,6 +1818,9 @@
       <x:c r="H84" s="43" t="str">
         <x:f>IF(D84=40,200,IF(D84=30,150,""))</x:f>
       </x:c>
+      <x:c r="I84" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="17"/>
@@ -1579,6 +1833,9 @@
       <x:c r="H85" s="43" t="str">
         <x:f>IF(D85=40,200,IF(D85=30,150,""))</x:f>
       </x:c>
+      <x:c r="I85" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="17"/>
@@ -1591,6 +1848,9 @@
       <x:c r="H86" s="43" t="str">
         <x:f>IF(D86=40,200,IF(D86=30,150,""))</x:f>
       </x:c>
+      <x:c r="I86" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="17"/>
@@ -1603,6 +1863,9 @@
       <x:c r="H87" s="43" t="str">
         <x:f>IF(D87=40,200,IF(D87=30,150,""))</x:f>
       </x:c>
+      <x:c r="I87" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="17"/>
@@ -1615,6 +1878,9 @@
       <x:c r="H88" s="43" t="str">
         <x:f>IF(D88=40,200,IF(D88=30,150,""))</x:f>
       </x:c>
+      <x:c r="I88" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="17"/>
@@ -1627,6 +1893,9 @@
       <x:c r="H89" s="43" t="str">
         <x:f>IF(D89=40,200,IF(D89=30,150,""))</x:f>
       </x:c>
+      <x:c r="I89" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="17"/>
@@ -1639,6 +1908,9 @@
       <x:c r="H90" s="43" t="str">
         <x:f>IF(D90=40,200,IF(D90=30,150,""))</x:f>
       </x:c>
+      <x:c r="I90" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="17"/>
@@ -1651,6 +1923,9 @@
       <x:c r="H91" s="43" t="str">
         <x:f>IF(D91=40,200,IF(D91=30,150,""))</x:f>
       </x:c>
+      <x:c r="I91" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="17"/>
@@ -1663,6 +1938,9 @@
       <x:c r="H92" s="43" t="str">
         <x:f>IF(D92=40,200,IF(D92=30,150,""))</x:f>
       </x:c>
+      <x:c r="I92" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="17"/>
@@ -1675,6 +1953,9 @@
       <x:c r="H93" s="43" t="str">
         <x:f>IF(D93=40,200,IF(D93=30,150,""))</x:f>
       </x:c>
+      <x:c r="I93" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="17"/>
@@ -1687,6 +1968,9 @@
       <x:c r="H94" s="43" t="str">
         <x:f>IF(D94=40,200,IF(D94=30,150,""))</x:f>
       </x:c>
+      <x:c r="I94" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="17"/>
@@ -1699,6 +1983,9 @@
       <x:c r="H95" s="43" t="str">
         <x:f>IF(D95=40,200,IF(D95=30,150,""))</x:f>
       </x:c>
+      <x:c r="I95" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="17"/>
@@ -1711,6 +1998,9 @@
       <x:c r="H96" s="43" t="str">
         <x:f>IF(D96=40,200,IF(D96=30,150,""))</x:f>
       </x:c>
+      <x:c r="I96" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="17"/>
@@ -1723,6 +2013,9 @@
       <x:c r="H97" s="43" t="str">
         <x:f>IF(D97=40,200,IF(D97=30,150,""))</x:f>
       </x:c>
+      <x:c r="I97" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="17"/>
@@ -1735,6 +2028,9 @@
       <x:c r="H98" s="43" t="str">
         <x:f>IF(D98=40,200,IF(D98=30,150,""))</x:f>
       </x:c>
+      <x:c r="I98" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="17"/>
@@ -1747,6 +2043,9 @@
       <x:c r="H99" s="43" t="str">
         <x:f>IF(D99=40,200,IF(D99=30,150,""))</x:f>
       </x:c>
+      <x:c r="I99" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="17"/>
@@ -1759,6 +2058,9 @@
       <x:c r="H100" s="43" t="str">
         <x:f>IF(D100=40,200,IF(D100=30,150,""))</x:f>
       </x:c>
+      <x:c r="I100" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="17"/>
@@ -1771,6 +2073,9 @@
       <x:c r="H101" s="43" t="str">
         <x:f>IF(D101=40,200,IF(D101=30,150,""))</x:f>
       </x:c>
+      <x:c r="I101" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="17"/>
@@ -1783,6 +2088,9 @@
       <x:c r="H102" s="43" t="str">
         <x:f>IF(D102=40,200,IF(D102=30,150,""))</x:f>
       </x:c>
+      <x:c r="I102" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="17"/>
@@ -1795,6 +2103,9 @@
       <x:c r="H103" s="43" t="str">
         <x:f>IF(D103=40,200,IF(D103=30,150,""))</x:f>
       </x:c>
+      <x:c r="I103" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="17"/>
@@ -1807,6 +2118,9 @@
       <x:c r="H104" s="43" t="str">
         <x:f>IF(D104=40,200,IF(D104=30,150,""))</x:f>
       </x:c>
+      <x:c r="I104" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="17"/>
@@ -1819,6 +2133,9 @@
       <x:c r="H105" s="43" t="str">
         <x:f>IF(D105=40,200,IF(D105=30,150,""))</x:f>
       </x:c>
+      <x:c r="I105" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="17"/>
@@ -1831,6 +2148,9 @@
       <x:c r="H106" s="43" t="str">
         <x:f>IF(D106=40,200,IF(D106=30,150,""))</x:f>
       </x:c>
+      <x:c r="I106" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="17"/>
@@ -1843,6 +2163,9 @@
       <x:c r="H107" s="43" t="str">
         <x:f>IF(D107=40,200,IF(D107=30,150,""))</x:f>
       </x:c>
+      <x:c r="I107" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="17"/>
@@ -1855,6 +2178,9 @@
       <x:c r="H108" s="43" t="str">
         <x:f>IF(D108=40,200,IF(D108=30,150,""))</x:f>
       </x:c>
+      <x:c r="I108" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="17"/>
@@ -1867,6 +2193,9 @@
       <x:c r="H109" s="43" t="str">
         <x:f>IF(D109=40,200,IF(D109=30,150,""))</x:f>
       </x:c>
+      <x:c r="I109" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="17"/>
@@ -1879,6 +2208,9 @@
       <x:c r="H110" s="43" t="str">
         <x:f>IF(D110=40,200,IF(D110=30,150,""))</x:f>
       </x:c>
+      <x:c r="I110" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="17"/>
@@ -1891,6 +2223,9 @@
       <x:c r="H111" s="43" t="str">
         <x:f>IF(D111=40,200,IF(D111=30,150,""))</x:f>
       </x:c>
+      <x:c r="I111" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="17"/>
@@ -1903,6 +2238,9 @@
       <x:c r="H112" s="43" t="str">
         <x:f>IF(D112=40,200,IF(D112=30,150,""))</x:f>
       </x:c>
+      <x:c r="I112" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="17"/>
@@ -1915,6 +2253,9 @@
       <x:c r="H113" s="43" t="str">
         <x:f>IF(D113=40,200,IF(D113=30,150,""))</x:f>
       </x:c>
+      <x:c r="I113" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="17"/>
@@ -1927,6 +2268,9 @@
       <x:c r="H114" s="43" t="str">
         <x:f>IF(D114=40,200,IF(D114=30,150,""))</x:f>
       </x:c>
+      <x:c r="I114" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="17"/>
@@ -1939,6 +2283,9 @@
       <x:c r="H115" s="43" t="str">
         <x:f>IF(D115=40,200,IF(D115=30,150,""))</x:f>
       </x:c>
+      <x:c r="I115" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="17"/>
@@ -1951,6 +2298,9 @@
       <x:c r="H116" s="43" t="str">
         <x:f>IF(D116=40,200,IF(D116=30,150,""))</x:f>
       </x:c>
+      <x:c r="I116" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="17"/>
@@ -1963,6 +2313,9 @@
       <x:c r="H117" s="43" t="str">
         <x:f>IF(D117=40,200,IF(D117=30,150,""))</x:f>
       </x:c>
+      <x:c r="I117" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="17"/>
@@ -1975,6 +2328,9 @@
       <x:c r="H118" s="43" t="str">
         <x:f>IF(D118=40,200,IF(D118=30,150,""))</x:f>
       </x:c>
+      <x:c r="I118" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="17"/>
@@ -1987,6 +2343,9 @@
       <x:c r="H119" s="43" t="str">
         <x:f>IF(D119=40,200,IF(D119=30,150,""))</x:f>
       </x:c>
+      <x:c r="I119" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="17"/>
@@ -1999,6 +2358,9 @@
       <x:c r="H120" s="43" t="str">
         <x:f>IF(D120=40,200,IF(D120=30,150,""))</x:f>
       </x:c>
+      <x:c r="I120" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="17"/>
@@ -2011,6 +2373,9 @@
       <x:c r="H121" s="43" t="str">
         <x:f>IF(D121=40,200,IF(D121=30,150,""))</x:f>
       </x:c>
+      <x:c r="I121" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="17"/>
@@ -2023,6 +2388,9 @@
       <x:c r="H122" s="43" t="str">
         <x:f>IF(D122=40,200,IF(D122=30,150,""))</x:f>
       </x:c>
+      <x:c r="I122" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="17"/>
@@ -2035,6 +2403,9 @@
       <x:c r="H123" s="43" t="str">
         <x:f>IF(D123=40,200,IF(D123=30,150,""))</x:f>
       </x:c>
+      <x:c r="I123" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="17"/>
@@ -2047,6 +2418,9 @@
       <x:c r="H124" s="43" t="str">
         <x:f>IF(D124=40,200,IF(D124=30,150,""))</x:f>
       </x:c>
+      <x:c r="I124" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="17"/>
@@ -2059,6 +2433,9 @@
       <x:c r="H125" s="43" t="str">
         <x:f>IF(D125=40,200,IF(D125=30,150,""))</x:f>
       </x:c>
+      <x:c r="I125" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="17"/>
@@ -2071,6 +2448,9 @@
       <x:c r="H126" s="43" t="str">
         <x:f>IF(D126=40,200,IF(D126=30,150,""))</x:f>
       </x:c>
+      <x:c r="I126" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="17"/>
@@ -2083,6 +2463,9 @@
       <x:c r="H127" s="43" t="str">
         <x:f>IF(D127=40,200,IF(D127=30,150,""))</x:f>
       </x:c>
+      <x:c r="I127" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="17"/>
@@ -2095,6 +2478,9 @@
       <x:c r="H128" s="43" t="str">
         <x:f>IF(D128=40,200,IF(D128=30,150,""))</x:f>
       </x:c>
+      <x:c r="I128" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="17"/>
@@ -2107,6 +2493,9 @@
       <x:c r="H129" s="43" t="str">
         <x:f>IF(D129=40,200,IF(D129=30,150,""))</x:f>
       </x:c>
+      <x:c r="I129" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="17"/>
@@ -2119,6 +2508,9 @@
       <x:c r="H130" s="43" t="str">
         <x:f>IF(D130=40,200,IF(D130=30,150,""))</x:f>
       </x:c>
+      <x:c r="I130" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="17"/>
@@ -2131,6 +2523,9 @@
       <x:c r="H131" s="43" t="str">
         <x:f>IF(D131=40,200,IF(D131=30,150,""))</x:f>
       </x:c>
+      <x:c r="I131" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="17"/>
@@ -2143,6 +2538,9 @@
       <x:c r="H132" s="43" t="str">
         <x:f>IF(D132=40,200,IF(D132=30,150,""))</x:f>
       </x:c>
+      <x:c r="I132" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="17"/>
@@ -2155,6 +2553,9 @@
       <x:c r="H133" s="43" t="str">
         <x:f>IF(D133=40,200,IF(D133=30,150,""))</x:f>
       </x:c>
+      <x:c r="I133" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="17"/>
@@ -2167,6 +2568,9 @@
       <x:c r="H134" s="43" t="str">
         <x:f>IF(D134=40,200,IF(D134=30,150,""))</x:f>
       </x:c>
+      <x:c r="I134" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="17"/>
@@ -2179,6 +2583,9 @@
       <x:c r="H135" s="43" t="str">
         <x:f>IF(D135=40,200,IF(D135=30,150,""))</x:f>
       </x:c>
+      <x:c r="I135" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="17"/>
@@ -2191,6 +2598,9 @@
       <x:c r="H136" s="43" t="str">
         <x:f>IF(D136=40,200,IF(D136=30,150,""))</x:f>
       </x:c>
+      <x:c r="I136" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="17"/>
@@ -2203,6 +2613,9 @@
       <x:c r="H137" s="43" t="str">
         <x:f>IF(D137=40,200,IF(D137=30,150,""))</x:f>
       </x:c>
+      <x:c r="I137" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="17"/>
@@ -2215,6 +2628,9 @@
       <x:c r="H138" s="43" t="str">
         <x:f>IF(D138=40,200,IF(D138=30,150,""))</x:f>
       </x:c>
+      <x:c r="I138" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="17"/>
@@ -2227,6 +2643,9 @@
       <x:c r="H139" s="43" t="str">
         <x:f>IF(D139=40,200,IF(D139=30,150,""))</x:f>
       </x:c>
+      <x:c r="I139" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="17"/>
@@ -2239,6 +2658,9 @@
       <x:c r="H140" s="43" t="str">
         <x:f>IF(D140=40,200,IF(D140=30,150,""))</x:f>
       </x:c>
+      <x:c r="I140" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="17"/>
@@ -2251,6 +2673,9 @@
       <x:c r="H141" s="43" t="str">
         <x:f>IF(D141=40,200,IF(D141=30,150,""))</x:f>
       </x:c>
+      <x:c r="I141" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="17"/>
@@ -2263,6 +2688,9 @@
       <x:c r="H142" s="43" t="str">
         <x:f>IF(D142=40,200,IF(D142=30,150,""))</x:f>
       </x:c>
+      <x:c r="I142" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="17"/>
@@ -2275,6 +2703,9 @@
       <x:c r="H143" s="43" t="str">
         <x:f>IF(D143=40,200,IF(D143=30,150,""))</x:f>
       </x:c>
+      <x:c r="I143" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="17"/>
@@ -2287,6 +2718,9 @@
       <x:c r="H144" s="43" t="str">
         <x:f>IF(D144=40,200,IF(D144=30,150,""))</x:f>
       </x:c>
+      <x:c r="I144" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="17"/>
@@ -2299,6 +2733,9 @@
       <x:c r="H145" s="43" t="str">
         <x:f>IF(D145=40,200,IF(D145=30,150,""))</x:f>
       </x:c>
+      <x:c r="I145" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="17"/>
@@ -2311,6 +2748,9 @@
       <x:c r="H146" s="43" t="str">
         <x:f>IF(D146=40,200,IF(D146=30,150,""))</x:f>
       </x:c>
+      <x:c r="I146" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="17"/>
@@ -2323,6 +2763,9 @@
       <x:c r="H147" s="43" t="str">
         <x:f>IF(D147=40,200,IF(D147=30,150,""))</x:f>
       </x:c>
+      <x:c r="I147" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="17"/>
@@ -2335,6 +2778,9 @@
       <x:c r="H148" s="43" t="str">
         <x:f>IF(D148=40,200,IF(D148=30,150,""))</x:f>
       </x:c>
+      <x:c r="I148" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="17"/>
@@ -2347,6 +2793,9 @@
       <x:c r="H149" s="43" t="str">
         <x:f>IF(D149=40,200,IF(D149=30,150,""))</x:f>
       </x:c>
+      <x:c r="I149" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="17"/>
@@ -2359,6 +2808,9 @@
       <x:c r="H150" s="43" t="str">
         <x:f>IF(D150=40,200,IF(D150=30,150,""))</x:f>
       </x:c>
+      <x:c r="I150" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="17"/>
@@ -2371,6 +2823,9 @@
       <x:c r="H151" s="43" t="str">
         <x:f>IF(D151=40,200,IF(D151=30,150,""))</x:f>
       </x:c>
+      <x:c r="I151" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="17"/>
@@ -2383,6 +2838,9 @@
       <x:c r="H152" s="43" t="str">
         <x:f>IF(D152=40,200,IF(D152=30,150,""))</x:f>
       </x:c>
+      <x:c r="I152" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="17"/>
@@ -2395,6 +2853,9 @@
       <x:c r="H153" s="43" t="str">
         <x:f>IF(D153=40,200,IF(D153=30,150,""))</x:f>
       </x:c>
+      <x:c r="I153" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="17"/>
@@ -2407,6 +2868,9 @@
       <x:c r="H154" s="43" t="str">
         <x:f>IF(D154=40,200,IF(D154=30,150,""))</x:f>
       </x:c>
+      <x:c r="I154" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="17"/>
@@ -2419,6 +2883,9 @@
       <x:c r="H155" s="43" t="str">
         <x:f>IF(D155=40,200,IF(D155=30,150,""))</x:f>
       </x:c>
+      <x:c r="I155" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="17"/>
@@ -2431,6 +2898,9 @@
       <x:c r="H156" s="43" t="str">
         <x:f>IF(D156=40,200,IF(D156=30,150,""))</x:f>
       </x:c>
+      <x:c r="I156" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="17"/>
@@ -2443,6 +2913,9 @@
       <x:c r="H157" s="43" t="str">
         <x:f>IF(D157=40,200,IF(D157=30,150,""))</x:f>
       </x:c>
+      <x:c r="I157" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="17"/>
@@ -2455,6 +2928,9 @@
       <x:c r="H158" s="43" t="str">
         <x:f>IF(D158=40,200,IF(D158=30,150,""))</x:f>
       </x:c>
+      <x:c r="I158" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="17"/>
@@ -2467,6 +2943,9 @@
       <x:c r="H159" s="43" t="str">
         <x:f>IF(D159=40,200,IF(D159=30,150,""))</x:f>
       </x:c>
+      <x:c r="I159" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="17"/>
@@ -2479,6 +2958,9 @@
       <x:c r="H160" s="43" t="str">
         <x:f>IF(D160=40,200,IF(D160=30,150,""))</x:f>
       </x:c>
+      <x:c r="I160" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="17"/>
@@ -2491,6 +2973,9 @@
       <x:c r="H161" s="43" t="str">
         <x:f>IF(D161=40,200,IF(D161=30,150,""))</x:f>
       </x:c>
+      <x:c r="I161" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="17"/>
@@ -2503,6 +2988,9 @@
       <x:c r="H162" s="43" t="str">
         <x:f>IF(D162=40,200,IF(D162=30,150,""))</x:f>
       </x:c>
+      <x:c r="I162" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="17"/>
@@ -2515,6 +3003,9 @@
       <x:c r="H163" s="43" t="str">
         <x:f>IF(D163=40,200,IF(D163=30,150,""))</x:f>
       </x:c>
+      <x:c r="I163" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="17"/>
@@ -2527,6 +3018,9 @@
       <x:c r="H164" s="43" t="str">
         <x:f>IF(D164=40,200,IF(D164=30,150,""))</x:f>
       </x:c>
+      <x:c r="I164" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="17"/>
@@ -2539,6 +3033,9 @@
       <x:c r="H165" s="43" t="str">
         <x:f>IF(D165=40,200,IF(D165=30,150,""))</x:f>
       </x:c>
+      <x:c r="I165" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="17"/>
@@ -2551,6 +3048,9 @@
       <x:c r="H166" s="43" t="str">
         <x:f>IF(D166=40,200,IF(D166=30,150,""))</x:f>
       </x:c>
+      <x:c r="I166" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="17"/>
@@ -2563,6 +3063,9 @@
       <x:c r="H167" s="43" t="str">
         <x:f>IF(D167=40,200,IF(D167=30,150,""))</x:f>
       </x:c>
+      <x:c r="I167" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="17"/>
@@ -2575,6 +3078,9 @@
       <x:c r="H168" s="43" t="str">
         <x:f>IF(D168=40,200,IF(D168=30,150,""))</x:f>
       </x:c>
+      <x:c r="I168" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="17"/>
@@ -2587,6 +3093,9 @@
       <x:c r="H169" s="43" t="str">
         <x:f>IF(D169=40,200,IF(D169=30,150,""))</x:f>
       </x:c>
+      <x:c r="I169" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="17"/>
@@ -2599,6 +3108,9 @@
       <x:c r="H170" s="43" t="str">
         <x:f>IF(D170=40,200,IF(D170=30,150,""))</x:f>
       </x:c>
+      <x:c r="I170" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="17"/>
@@ -2611,6 +3123,9 @@
       <x:c r="H171" s="43" t="str">
         <x:f>IF(D171=40,200,IF(D171=30,150,""))</x:f>
       </x:c>
+      <x:c r="I171" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="17"/>
@@ -2623,6 +3138,9 @@
       <x:c r="H172" s="43" t="str">
         <x:f>IF(D172=40,200,IF(D172=30,150,""))</x:f>
       </x:c>
+      <x:c r="I172" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="17"/>
@@ -2635,6 +3153,9 @@
       <x:c r="H173" s="43" t="str">
         <x:f>IF(D173=40,200,IF(D173=30,150,""))</x:f>
       </x:c>
+      <x:c r="I173" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="17"/>
@@ -2647,6 +3168,9 @@
       <x:c r="H174" s="43" t="str">
         <x:f>IF(D174=40,200,IF(D174=30,150,""))</x:f>
       </x:c>
+      <x:c r="I174" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="17"/>
@@ -2659,6 +3183,9 @@
       <x:c r="H175" s="43" t="str">
         <x:f>IF(D175=40,200,IF(D175=30,150,""))</x:f>
       </x:c>
+      <x:c r="I175" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="17"/>
@@ -2671,6 +3198,9 @@
       <x:c r="H176" s="43" t="str">
         <x:f>IF(D176=40,200,IF(D176=30,150,""))</x:f>
       </x:c>
+      <x:c r="I176" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="17"/>
@@ -2683,6 +3213,9 @@
       <x:c r="H177" s="43" t="str">
         <x:f>IF(D177=40,200,IF(D177=30,150,""))</x:f>
       </x:c>
+      <x:c r="I177" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="17"/>
@@ -2695,6 +3228,9 @@
       <x:c r="H178" s="43" t="str">
         <x:f>IF(D178=40,200,IF(D178=30,150,""))</x:f>
       </x:c>
+      <x:c r="I178" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="17"/>
@@ -2707,6 +3243,9 @@
       <x:c r="H179" s="43" t="str">
         <x:f>IF(D179=40,200,IF(D179=30,150,""))</x:f>
       </x:c>
+      <x:c r="I179" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="17"/>
@@ -2719,6 +3258,9 @@
       <x:c r="H180" s="43" t="str">
         <x:f>IF(D180=40,200,IF(D180=30,150,""))</x:f>
       </x:c>
+      <x:c r="I180" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="17"/>
@@ -2731,6 +3273,9 @@
       <x:c r="H181" s="43" t="str">
         <x:f>IF(D181=40,200,IF(D181=30,150,""))</x:f>
       </x:c>
+      <x:c r="I181" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="17"/>
@@ -2743,6 +3288,9 @@
       <x:c r="H182" s="43" t="str">
         <x:f>IF(D182=40,200,IF(D182=30,150,""))</x:f>
       </x:c>
+      <x:c r="I182" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="17"/>
@@ -2755,6 +3303,9 @@
       <x:c r="H183" s="43" t="str">
         <x:f>IF(D183=40,200,IF(D183=30,150,""))</x:f>
       </x:c>
+      <x:c r="I183" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="17"/>
@@ -2767,6 +3318,9 @@
       <x:c r="H184" s="43" t="str">
         <x:f>IF(D184=40,200,IF(D184=30,150,""))</x:f>
       </x:c>
+      <x:c r="I184" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="17"/>
@@ -2779,6 +3333,9 @@
       <x:c r="H185" s="43" t="str">
         <x:f>IF(D185=40,200,IF(D185=30,150,""))</x:f>
       </x:c>
+      <x:c r="I185" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="17"/>
@@ -2791,6 +3348,9 @@
       <x:c r="H186" s="43" t="str">
         <x:f>IF(D186=40,200,IF(D186=30,150,""))</x:f>
       </x:c>
+      <x:c r="I186" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="17"/>
@@ -2803,6 +3363,9 @@
       <x:c r="H187" s="43" t="str">
         <x:f>IF(D187=40,200,IF(D187=30,150,""))</x:f>
       </x:c>
+      <x:c r="I187" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="17"/>
@@ -2815,6 +3378,9 @@
       <x:c r="H188" s="43" t="str">
         <x:f>IF(D188=40,200,IF(D188=30,150,""))</x:f>
       </x:c>
+      <x:c r="I188" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="17"/>
@@ -2827,6 +3393,9 @@
       <x:c r="H189" s="43" t="str">
         <x:f>IF(D189=40,200,IF(D189=30,150,""))</x:f>
       </x:c>
+      <x:c r="I189" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="17"/>
@@ -2839,6 +3408,9 @@
       <x:c r="H190" s="43" t="str">
         <x:f>IF(D190=40,200,IF(D190=30,150,""))</x:f>
       </x:c>
+      <x:c r="I190" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="17"/>
@@ -2851,6 +3423,9 @@
       <x:c r="H191" s="43" t="str">
         <x:f>IF(D191=40,200,IF(D191=30,150,""))</x:f>
       </x:c>
+      <x:c r="I191" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="17"/>
@@ -2863,6 +3438,9 @@
       <x:c r="H192" s="43" t="str">
         <x:f>IF(D192=40,200,IF(D192=30,150,""))</x:f>
       </x:c>
+      <x:c r="I192" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="17"/>
@@ -2875,6 +3453,9 @@
       <x:c r="H193" s="43" t="str">
         <x:f>IF(D193=40,200,IF(D193=30,150,""))</x:f>
       </x:c>
+      <x:c r="I193" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="17"/>
@@ -2887,6 +3468,9 @@
       <x:c r="H194" s="43" t="str">
         <x:f>IF(D194=40,200,IF(D194=30,150,""))</x:f>
       </x:c>
+      <x:c r="I194" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="17"/>
@@ -2899,6 +3483,9 @@
       <x:c r="H195" s="43" t="str">
         <x:f>IF(D195=40,200,IF(D195=30,150,""))</x:f>
       </x:c>
+      <x:c r="I195" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="17"/>
@@ -2911,6 +3498,9 @@
       <x:c r="H196" s="43" t="str">
         <x:f>IF(D196=40,200,IF(D196=30,150,""))</x:f>
       </x:c>
+      <x:c r="I196" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="17"/>
@@ -2923,6 +3513,9 @@
       <x:c r="H197" s="43" t="str">
         <x:f>IF(D197=40,200,IF(D197=30,150,""))</x:f>
       </x:c>
+      <x:c r="I197" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="17"/>
@@ -2935,6 +3528,9 @@
       <x:c r="H198" s="43" t="str">
         <x:f>IF(D198=40,200,IF(D198=30,150,""))</x:f>
       </x:c>
+      <x:c r="I198" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="17"/>
@@ -2947,6 +3543,9 @@
       <x:c r="H199" s="43" t="str">
         <x:f>IF(D199=40,200,IF(D199=30,150,""))</x:f>
       </x:c>
+      <x:c r="I199" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="17"/>
@@ -2959,6 +3558,9 @@
       <x:c r="H200" s="43" t="str">
         <x:f>IF(D200=40,200,IF(D200=30,150,""))</x:f>
       </x:c>
+      <x:c r="I200" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="17"/>
@@ -2971,6 +3573,9 @@
       <x:c r="H201" s="43" t="str">
         <x:f>IF(D201=40,200,IF(D201=30,150,""))</x:f>
       </x:c>
+      <x:c r="I201" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="17"/>
@@ -2983,6 +3588,9 @@
       <x:c r="H202" s="43" t="str">
         <x:f>IF(D202=40,200,IF(D202=30,150,""))</x:f>
       </x:c>
+      <x:c r="I202" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="17"/>
@@ -2995,6 +3603,9 @@
       <x:c r="H203" s="43" t="str">
         <x:f>IF(D203=40,200,IF(D203=30,150,""))</x:f>
       </x:c>
+      <x:c r="I203" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="17"/>
@@ -3007,6 +3618,9 @@
       <x:c r="H204" s="43" t="str">
         <x:f>IF(D204=40,200,IF(D204=30,150,""))</x:f>
       </x:c>
+      <x:c r="I204" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="17"/>
@@ -3019,6 +3633,9 @@
       <x:c r="H205" s="43" t="str">
         <x:f>IF(D205=40,200,IF(D205=30,150,""))</x:f>
       </x:c>
+      <x:c r="I205" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="17"/>
@@ -3031,6 +3648,9 @@
       <x:c r="H206" s="43" t="str">
         <x:f>IF(D206=40,200,IF(D206=30,150,""))</x:f>
       </x:c>
+      <x:c r="I206" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="17"/>
@@ -3043,6 +3663,9 @@
       <x:c r="H207" s="43" t="str">
         <x:f>IF(D207=40,200,IF(D207=30,150,""))</x:f>
       </x:c>
+      <x:c r="I207" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="17"/>
@@ -3055,6 +3678,9 @@
       <x:c r="H208" s="43" t="str">
         <x:f>IF(D208=40,200,IF(D208=30,150,""))</x:f>
       </x:c>
+      <x:c r="I208" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="17"/>
@@ -3067,6 +3693,9 @@
       <x:c r="H209" s="43" t="str">
         <x:f>IF(D209=40,200,IF(D209=30,150,""))</x:f>
       </x:c>
+      <x:c r="I209" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="17"/>
@@ -3079,6 +3708,9 @@
       <x:c r="H210" s="43" t="str">
         <x:f>IF(D210=40,200,IF(D210=30,150,""))</x:f>
       </x:c>
+      <x:c r="I210" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="17"/>
@@ -3091,6 +3723,9 @@
       <x:c r="H211" s="43" t="str">
         <x:f>IF(D211=40,200,IF(D211=30,150,""))</x:f>
       </x:c>
+      <x:c r="I211" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="17"/>
@@ -3103,6 +3738,9 @@
       <x:c r="H212" s="43" t="str">
         <x:f>IF(D212=40,200,IF(D212=30,150,""))</x:f>
       </x:c>
+      <x:c r="I212" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="17"/>
@@ -3115,6 +3753,9 @@
       <x:c r="H213" s="43" t="str">
         <x:f>IF(D213=40,200,IF(D213=30,150,""))</x:f>
       </x:c>
+      <x:c r="I213" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="17"/>
@@ -3127,6 +3768,9 @@
       <x:c r="H214" s="43" t="str">
         <x:f>IF(D214=40,200,IF(D214=30,150,""))</x:f>
       </x:c>
+      <x:c r="I214" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="17"/>
@@ -3139,6 +3783,9 @@
       <x:c r="H215" s="43" t="str">
         <x:f>IF(D215=40,200,IF(D215=30,150,""))</x:f>
       </x:c>
+      <x:c r="I215" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="17"/>
@@ -3151,6 +3798,9 @@
       <x:c r="H216" s="43" t="str">
         <x:f>IF(D216=40,200,IF(D216=30,150,""))</x:f>
       </x:c>
+      <x:c r="I216" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="17"/>
@@ -3163,6 +3813,9 @@
       <x:c r="H217" s="43" t="str">
         <x:f>IF(D217=40,200,IF(D217=30,150,""))</x:f>
       </x:c>
+      <x:c r="I217" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="17"/>
@@ -3175,6 +3828,9 @@
       <x:c r="H218" s="43" t="str">
         <x:f>IF(D218=40,200,IF(D218=30,150,""))</x:f>
       </x:c>
+      <x:c r="I218" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="17"/>
@@ -3187,6 +3843,9 @@
       <x:c r="H219" s="43" t="str">
         <x:f>IF(D219=40,200,IF(D219=30,150,""))</x:f>
       </x:c>
+      <x:c r="I219" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="17"/>
@@ -3199,6 +3858,9 @@
       <x:c r="H220" s="43" t="str">
         <x:f>IF(D220=40,200,IF(D220=30,150,""))</x:f>
       </x:c>
+      <x:c r="I220" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="17"/>
@@ -3211,6 +3873,9 @@
       <x:c r="H221" s="43" t="str">
         <x:f>IF(D221=40,200,IF(D221=30,150,""))</x:f>
       </x:c>
+      <x:c r="I221" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="17"/>
@@ -3223,6 +3888,9 @@
       <x:c r="H222" s="43" t="str">
         <x:f>IF(D222=40,200,IF(D222=30,150,""))</x:f>
       </x:c>
+      <x:c r="I222" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="17"/>
@@ -3235,6 +3903,9 @@
       <x:c r="H223" s="43" t="str">
         <x:f>IF(D223=40,200,IF(D223=30,150,""))</x:f>
       </x:c>
+      <x:c r="I223" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="17"/>
@@ -3247,6 +3918,9 @@
       <x:c r="H224" s="43" t="str">
         <x:f>IF(D224=40,200,IF(D224=30,150,""))</x:f>
       </x:c>
+      <x:c r="I224" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="17"/>
@@ -3259,6 +3933,9 @@
       <x:c r="H225" s="43" t="str">
         <x:f>IF(D225=40,200,IF(D225=30,150,""))</x:f>
       </x:c>
+      <x:c r="I225" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="17"/>
@@ -3271,6 +3948,9 @@
       <x:c r="H226" s="43" t="str">
         <x:f>IF(D226=40,200,IF(D226=30,150,""))</x:f>
       </x:c>
+      <x:c r="I226" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="17"/>
@@ -3283,6 +3963,9 @@
       <x:c r="H227" s="43" t="str">
         <x:f>IF(D227=40,200,IF(D227=30,150,""))</x:f>
       </x:c>
+      <x:c r="I227" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="17"/>
@@ -3295,6 +3978,9 @@
       <x:c r="H228" s="43" t="str">
         <x:f>IF(D228=40,200,IF(D228=30,150,""))</x:f>
       </x:c>
+      <x:c r="I228" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="17"/>
@@ -3307,6 +3993,9 @@
       <x:c r="H229" s="43" t="str">
         <x:f>IF(D229=40,200,IF(D229=30,150,""))</x:f>
       </x:c>
+      <x:c r="I229" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="17"/>
@@ -3319,6 +4008,9 @@
       <x:c r="H230" s="43" t="str">
         <x:f>IF(D230=40,200,IF(D230=30,150,""))</x:f>
       </x:c>
+      <x:c r="I230" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="17"/>
@@ -3331,6 +4023,9 @@
       <x:c r="H231" s="43" t="str">
         <x:f>IF(D231=40,200,IF(D231=30,150,""))</x:f>
       </x:c>
+      <x:c r="I231" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="17"/>
@@ -3343,6 +4038,9 @@
       <x:c r="H232" s="43" t="str">
         <x:f>IF(D232=40,200,IF(D232=30,150,""))</x:f>
       </x:c>
+      <x:c r="I232" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="17"/>
@@ -3355,6 +4053,9 @@
       <x:c r="H233" s="43" t="str">
         <x:f>IF(D233=40,200,IF(D233=30,150,""))</x:f>
       </x:c>
+      <x:c r="I233" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="17"/>
@@ -3367,6 +4068,9 @@
       <x:c r="H234" s="43" t="str">
         <x:f>IF(D234=40,200,IF(D234=30,150,""))</x:f>
       </x:c>
+      <x:c r="I234" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="17"/>
@@ -3379,6 +4083,9 @@
       <x:c r="H235" s="43" t="str">
         <x:f>IF(D235=40,200,IF(D235=30,150,""))</x:f>
       </x:c>
+      <x:c r="I235" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="17"/>
@@ -3391,6 +4098,9 @@
       <x:c r="H236" s="43" t="str">
         <x:f>IF(D236=40,200,IF(D236=30,150,""))</x:f>
       </x:c>
+      <x:c r="I236" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="17"/>
@@ -3403,6 +4113,9 @@
       <x:c r="H237" s="43" t="str">
         <x:f>IF(D237=40,200,IF(D237=30,150,""))</x:f>
       </x:c>
+      <x:c r="I237" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="17"/>
@@ -3415,6 +4128,9 @@
       <x:c r="H238" s="43" t="str">
         <x:f>IF(D238=40,200,IF(D238=30,150,""))</x:f>
       </x:c>
+      <x:c r="I238" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="17"/>
@@ -3427,6 +4143,9 @@
       <x:c r="H239" s="43" t="str">
         <x:f>IF(D239=40,200,IF(D239=30,150,""))</x:f>
       </x:c>
+      <x:c r="I239" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="17"/>
@@ -3439,6 +4158,9 @@
       <x:c r="H240" s="43" t="str">
         <x:f>IF(D240=40,200,IF(D240=30,150,""))</x:f>
       </x:c>
+      <x:c r="I240" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="17"/>
@@ -3451,6 +4173,9 @@
       <x:c r="H241" s="43" t="str">
         <x:f>IF(D241=40,200,IF(D241=30,150,""))</x:f>
       </x:c>
+      <x:c r="I241" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="17"/>
@@ -3463,6 +4188,9 @@
       <x:c r="H242" s="43" t="str">
         <x:f>IF(D242=40,200,IF(D242=30,150,""))</x:f>
       </x:c>
+      <x:c r="I242" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="17"/>
@@ -3475,6 +4203,9 @@
       <x:c r="H243" s="43" t="str">
         <x:f>IF(D243=40,200,IF(D243=30,150,""))</x:f>
       </x:c>
+      <x:c r="I243" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="17"/>
@@ -3487,6 +4218,9 @@
       <x:c r="H244" s="43" t="str">
         <x:f>IF(D244=40,200,IF(D244=30,150,""))</x:f>
       </x:c>
+      <x:c r="I244" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="17"/>
@@ -3499,6 +4233,9 @@
       <x:c r="H245" s="43" t="str">
         <x:f>IF(D245=40,200,IF(D245=30,150,""))</x:f>
       </x:c>
+      <x:c r="I245" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="17"/>
@@ -3511,6 +4248,9 @@
       <x:c r="H246" s="43" t="str">
         <x:f>IF(D246=40,200,IF(D246=30,150,""))</x:f>
       </x:c>
+      <x:c r="I246" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="17"/>
@@ -3523,6 +4263,9 @@
       <x:c r="H247" s="43" t="str">
         <x:f>IF(D247=40,200,IF(D247=30,150,""))</x:f>
       </x:c>
+      <x:c r="I247" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="17"/>
@@ -3535,6 +4278,9 @@
       <x:c r="H248" s="43" t="str">
         <x:f>IF(D248=40,200,IF(D248=30,150,""))</x:f>
       </x:c>
+      <x:c r="I248" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="17"/>
@@ -3547,6 +4293,9 @@
       <x:c r="H249" s="43" t="str">
         <x:f>IF(D249=40,200,IF(D249=30,150,""))</x:f>
       </x:c>
+      <x:c r="I249" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="17"/>
@@ -3559,6 +4308,9 @@
       <x:c r="H250" s="43" t="str">
         <x:f>IF(D250=40,200,IF(D250=30,150,""))</x:f>
       </x:c>
+      <x:c r="I250" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="17"/>
@@ -3571,6 +4323,9 @@
       <x:c r="H251" s="43" t="str">
         <x:f>IF(D251=40,200,IF(D251=30,150,""))</x:f>
       </x:c>
+      <x:c r="I251" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="17"/>
@@ -3583,6 +4338,9 @@
       <x:c r="H252" s="43" t="str">
         <x:f>IF(D252=40,200,IF(D252=30,150,""))</x:f>
       </x:c>
+      <x:c r="I252" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="17"/>
@@ -3595,6 +4353,9 @@
       <x:c r="H253" s="43" t="str">
         <x:f>IF(D253=40,200,IF(D253=30,150,""))</x:f>
       </x:c>
+      <x:c r="I253" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="17"/>
@@ -3607,6 +4368,9 @@
       <x:c r="H254" s="43" t="str">
         <x:f>IF(D254=40,200,IF(D254=30,150,""))</x:f>
       </x:c>
+      <x:c r="I254" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="17"/>
@@ -3619,6 +4383,9 @@
       <x:c r="H255" s="43" t="str">
         <x:f>IF(D255=40,200,IF(D255=30,150,""))</x:f>
       </x:c>
+      <x:c r="I255" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="17"/>
@@ -3631,6 +4398,9 @@
       <x:c r="H256" s="43" t="str">
         <x:f>IF(D256=40,200,IF(D256=30,150,""))</x:f>
       </x:c>
+      <x:c r="I256" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="17"/>
@@ -3643,6 +4413,9 @@
       <x:c r="H257" s="43" t="str">
         <x:f>IF(D257=40,200,IF(D257=30,150,""))</x:f>
       </x:c>
+      <x:c r="I257" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="17"/>
@@ -3655,6 +4428,9 @@
       <x:c r="H258" s="43" t="str">
         <x:f>IF(D258=40,200,IF(D258=30,150,""))</x:f>
       </x:c>
+      <x:c r="I258" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="17"/>
@@ -3667,6 +4443,9 @@
       <x:c r="H259" s="43" t="str">
         <x:f>IF(D259=40,200,IF(D259=30,150,""))</x:f>
       </x:c>
+      <x:c r="I259" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="17"/>
@@ -3679,6 +4458,9 @@
       <x:c r="H260" s="43" t="str">
         <x:f>IF(D260=40,200,IF(D260=30,150,""))</x:f>
       </x:c>
+      <x:c r="I260" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="17"/>
@@ -3691,6 +4473,9 @@
       <x:c r="H261" s="43" t="str">
         <x:f>IF(D261=40,200,IF(D261=30,150,""))</x:f>
       </x:c>
+      <x:c r="I261" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="17"/>
@@ -3703,6 +4488,9 @@
       <x:c r="H262" s="43" t="str">
         <x:f>IF(D262=40,200,IF(D262=30,150,""))</x:f>
       </x:c>
+      <x:c r="I262" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="17"/>
@@ -3715,6 +4503,9 @@
       <x:c r="H263" s="43" t="str">
         <x:f>IF(D263=40,200,IF(D263=30,150,""))</x:f>
       </x:c>
+      <x:c r="I263" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="17"/>
@@ -3727,6 +4518,9 @@
       <x:c r="H264" s="43" t="str">
         <x:f>IF(D264=40,200,IF(D264=30,150,""))</x:f>
       </x:c>
+      <x:c r="I264" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="17"/>
@@ -3739,6 +4533,9 @@
       <x:c r="H265" s="43" t="str">
         <x:f>IF(D265=40,200,IF(D265=30,150,""))</x:f>
       </x:c>
+      <x:c r="I265" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="17"/>
@@ -3751,6 +4548,9 @@
       <x:c r="H266" s="43" t="str">
         <x:f>IF(D266=40,200,IF(D266=30,150,""))</x:f>
       </x:c>
+      <x:c r="I266" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="17"/>
@@ -3763,6 +4563,9 @@
       <x:c r="H267" s="43" t="str">
         <x:f>IF(D267=40,200,IF(D267=30,150,""))</x:f>
       </x:c>
+      <x:c r="I267" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="17"/>
@@ -3775,6 +4578,9 @@
       <x:c r="H268" s="43" t="str">
         <x:f>IF(D268=40,200,IF(D268=30,150,""))</x:f>
       </x:c>
+      <x:c r="I268" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="17"/>
@@ -3787,6 +4593,9 @@
       <x:c r="H269" s="43" t="str">
         <x:f>IF(D269=40,200,IF(D269=30,150,""))</x:f>
       </x:c>
+      <x:c r="I269" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="17"/>
@@ -3799,6 +4608,9 @@
       <x:c r="H270" s="43" t="str">
         <x:f>IF(D270=40,200,IF(D270=30,150,""))</x:f>
       </x:c>
+      <x:c r="I270" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="17"/>
@@ -3811,6 +4623,9 @@
       <x:c r="H271" s="43" t="str">
         <x:f>IF(D271=40,200,IF(D271=30,150,""))</x:f>
       </x:c>
+      <x:c r="I271" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="17"/>
@@ -3823,6 +4638,9 @@
       <x:c r="H272" s="43" t="str">
         <x:f>IF(D272=40,200,IF(D272=30,150,""))</x:f>
       </x:c>
+      <x:c r="I272" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="17"/>
@@ -3835,6 +4653,9 @@
       <x:c r="H273" s="43" t="str">
         <x:f>IF(D273=40,200,IF(D273=30,150,""))</x:f>
       </x:c>
+      <x:c r="I273" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="17"/>
@@ -3847,6 +4668,9 @@
       <x:c r="H274" s="43" t="str">
         <x:f>IF(D274=40,200,IF(D274=30,150,""))</x:f>
       </x:c>
+      <x:c r="I274" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="17"/>
@@ -3859,6 +4683,9 @@
       <x:c r="H275" s="43" t="str">
         <x:f>IF(D275=40,200,IF(D275=30,150,""))</x:f>
       </x:c>
+      <x:c r="I275" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="17"/>
@@ -3871,6 +4698,9 @@
       <x:c r="H276" s="43" t="str">
         <x:f>IF(D276=40,200,IF(D276=30,150,""))</x:f>
       </x:c>
+      <x:c r="I276" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="17"/>
@@ -3883,6 +4713,9 @@
       <x:c r="H277" s="43" t="str">
         <x:f>IF(D277=40,200,IF(D277=30,150,""))</x:f>
       </x:c>
+      <x:c r="I277" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="17"/>
@@ -3895,6 +4728,9 @@
       <x:c r="H278" s="43" t="str">
         <x:f>IF(D278=40,200,IF(D278=30,150,""))</x:f>
       </x:c>
+      <x:c r="I278" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="17"/>
@@ -3907,6 +4743,9 @@
       <x:c r="H279" s="43" t="str">
         <x:f>IF(D279=40,200,IF(D279=30,150,""))</x:f>
       </x:c>
+      <x:c r="I279" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="17"/>
@@ -3919,6 +4758,9 @@
       <x:c r="H280" s="43" t="str">
         <x:f>IF(D280=40,200,IF(D280=30,150,""))</x:f>
       </x:c>
+      <x:c r="I280" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="17"/>
@@ -3931,6 +4773,9 @@
       <x:c r="H281" s="43" t="str">
         <x:f>IF(D281=40,200,IF(D281=30,150,""))</x:f>
       </x:c>
+      <x:c r="I281" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="17"/>
@@ -3943,6 +4788,9 @@
       <x:c r="H282" s="43" t="str">
         <x:f>IF(D282=40,200,IF(D282=30,150,""))</x:f>
       </x:c>
+      <x:c r="I282" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="17"/>
@@ -3955,6 +4803,9 @@
       <x:c r="H283" s="43" t="str">
         <x:f>IF(D283=40,200,IF(D283=30,150,""))</x:f>
       </x:c>
+      <x:c r="I283" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="17"/>
@@ -3967,6 +4818,9 @@
       <x:c r="H284" s="43" t="str">
         <x:f>IF(D284=40,200,IF(D284=30,150,""))</x:f>
       </x:c>
+      <x:c r="I284" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="17"/>
@@ -3979,6 +4833,9 @@
       <x:c r="H285" s="43" t="str">
         <x:f>IF(D285=40,200,IF(D285=30,150,""))</x:f>
       </x:c>
+      <x:c r="I285" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="17"/>
@@ -3991,6 +4848,9 @@
       <x:c r="H286" s="43" t="str">
         <x:f>IF(D286=40,200,IF(D286=30,150,""))</x:f>
       </x:c>
+      <x:c r="I286" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="17"/>
@@ -4003,6 +4863,9 @@
       <x:c r="H287" s="43" t="str">
         <x:f>IF(D287=40,200,IF(D287=30,150,""))</x:f>
       </x:c>
+      <x:c r="I287" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="17"/>
@@ -4015,6 +4878,9 @@
       <x:c r="H288" s="43" t="str">
         <x:f>IF(D288=40,200,IF(D288=30,150,""))</x:f>
       </x:c>
+      <x:c r="I288" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="17"/>
@@ -4027,6 +4893,9 @@
       <x:c r="H289" s="43" t="str">
         <x:f>IF(D289=40,200,IF(D289=30,150,""))</x:f>
       </x:c>
+      <x:c r="I289" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="17"/>
@@ -4039,6 +4908,9 @@
       <x:c r="H290" s="43" t="str">
         <x:f>IF(D290=40,200,IF(D290=30,150,""))</x:f>
       </x:c>
+      <x:c r="I290" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="17"/>
@@ -4051,6 +4923,9 @@
       <x:c r="H291" s="43" t="str">
         <x:f>IF(D291=40,200,IF(D291=30,150,""))</x:f>
       </x:c>
+      <x:c r="I291" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="17"/>
@@ -4063,6 +4938,9 @@
       <x:c r="H292" s="43" t="str">
         <x:f>IF(D292=40,200,IF(D292=30,150,""))</x:f>
       </x:c>
+      <x:c r="I292" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="17"/>
@@ -4075,6 +4953,9 @@
       <x:c r="H293" s="43" t="str">
         <x:f>IF(D293=40,200,IF(D293=30,150,""))</x:f>
       </x:c>
+      <x:c r="I293" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="17"/>
@@ -4087,6 +4968,9 @@
       <x:c r="H294" s="43" t="str">
         <x:f>IF(D294=40,200,IF(D294=30,150,""))</x:f>
       </x:c>
+      <x:c r="I294" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="17"/>
@@ -4099,6 +4983,9 @@
       <x:c r="H295" s="43" t="str">
         <x:f>IF(D295=40,200,IF(D295=30,150,""))</x:f>
       </x:c>
+      <x:c r="I295" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="17"/>
@@ -4111,6 +4998,9 @@
       <x:c r="H296" s="43" t="str">
         <x:f>IF(D296=40,200,IF(D296=30,150,""))</x:f>
       </x:c>
+      <x:c r="I296" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="17"/>
@@ -4123,6 +5013,9 @@
       <x:c r="H297" s="43" t="str">
         <x:f>IF(D297=40,200,IF(D297=30,150,""))</x:f>
       </x:c>
+      <x:c r="I297" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="17"/>
@@ -4135,6 +5028,9 @@
       <x:c r="H298" s="43" t="str">
         <x:f>IF(D298=40,200,IF(D298=30,150,""))</x:f>
       </x:c>
+      <x:c r="I298" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="17"/>
@@ -4147,6 +5043,9 @@
       <x:c r="H299" s="43" t="str">
         <x:f>IF(D299=40,200,IF(D299=30,150,""))</x:f>
       </x:c>
+      <x:c r="I299" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="17"/>
@@ -4159,6 +5058,9 @@
       <x:c r="H300" s="43" t="str">
         <x:f>IF(D300=40,200,IF(D300=30,150,""))</x:f>
       </x:c>
+      <x:c r="I300" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="17"/>
@@ -4171,6 +5073,9 @@
       <x:c r="H301" s="43" t="str">
         <x:f>IF(D301=40,200,IF(D301=30,150,""))</x:f>
       </x:c>
+      <x:c r="I301" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="17"/>
@@ -4183,6 +5088,9 @@
       <x:c r="H302" s="43" t="str">
         <x:f>IF(D302=40,200,IF(D302=30,150,""))</x:f>
       </x:c>
+      <x:c r="I302" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="17"/>
@@ -4195,6 +5103,9 @@
       <x:c r="H303" s="43" t="str">
         <x:f>IF(D303=40,200,IF(D303=30,150,""))</x:f>
       </x:c>
+      <x:c r="I303" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="17"/>
@@ -4207,6 +5118,9 @@
       <x:c r="H304" s="43" t="str">
         <x:f>IF(D304=40,200,IF(D304=30,150,""))</x:f>
       </x:c>
+      <x:c r="I304" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="17"/>
@@ -4219,6 +5133,9 @@
       <x:c r="H305" s="43" t="str">
         <x:f>IF(D305=40,200,IF(D305=30,150,""))</x:f>
       </x:c>
+      <x:c r="I305" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="17"/>
@@ -4231,6 +5148,9 @@
       <x:c r="H306" s="43" t="str">
         <x:f>IF(D306=40,200,IF(D306=30,150,""))</x:f>
       </x:c>
+      <x:c r="I306" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="17"/>
@@ -4243,6 +5163,9 @@
       <x:c r="H307" s="43" t="str">
         <x:f>IF(D307=40,200,IF(D307=30,150,""))</x:f>
       </x:c>
+      <x:c r="I307" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="17"/>
@@ -4255,6 +5178,9 @@
       <x:c r="H308" s="43" t="str">
         <x:f>IF(D308=40,200,IF(D308=30,150,""))</x:f>
       </x:c>
+      <x:c r="I308" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="17"/>
@@ -4267,6 +5193,9 @@
       <x:c r="H309" s="43" t="str">
         <x:f>IF(D309=40,200,IF(D309=30,150,""))</x:f>
       </x:c>
+      <x:c r="I309" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="17"/>
@@ -4279,6 +5208,9 @@
       <x:c r="H310" s="43" t="str">
         <x:f>IF(D310=40,200,IF(D310=30,150,""))</x:f>
       </x:c>
+      <x:c r="I310" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="17"/>
@@ -4291,6 +5223,9 @@
       <x:c r="H311" s="43" t="str">
         <x:f>IF(D311=40,200,IF(D311=30,150,""))</x:f>
       </x:c>
+      <x:c r="I311" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="17"/>
@@ -4303,6 +5238,9 @@
       <x:c r="H312" s="43" t="str">
         <x:f>IF(D312=40,200,IF(D312=30,150,""))</x:f>
       </x:c>
+      <x:c r="I312" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="17"/>
@@ -4315,6 +5253,9 @@
       <x:c r="H313" s="43" t="str">
         <x:f>IF(D313=40,200,IF(D313=30,150,""))</x:f>
       </x:c>
+      <x:c r="I313" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="17"/>
@@ -4327,6 +5268,9 @@
       <x:c r="H314" s="43" t="str">
         <x:f>IF(D314=40,200,IF(D314=30,150,""))</x:f>
       </x:c>
+      <x:c r="I314" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="17"/>
@@ -4339,6 +5283,9 @@
       <x:c r="H315" s="43" t="str">
         <x:f>IF(D315=40,200,IF(D315=30,150,""))</x:f>
       </x:c>
+      <x:c r="I315" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="17"/>
@@ -4351,6 +5298,9 @@
       <x:c r="H316" s="43" t="str">
         <x:f>IF(D316=40,200,IF(D316=30,150,""))</x:f>
       </x:c>
+      <x:c r="I316" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="17"/>
@@ -4363,6 +5313,9 @@
       <x:c r="H317" s="43" t="str">
         <x:f>IF(D317=40,200,IF(D317=30,150,""))</x:f>
       </x:c>
+      <x:c r="I317" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="17"/>
@@ -4375,6 +5328,9 @@
       <x:c r="H318" s="43" t="str">
         <x:f>IF(D318=40,200,IF(D318=30,150,""))</x:f>
       </x:c>
+      <x:c r="I318" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="17"/>
@@ -4387,6 +5343,9 @@
       <x:c r="H319" s="43" t="str">
         <x:f>IF(D319=40,200,IF(D319=30,150,""))</x:f>
       </x:c>
+      <x:c r="I319" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="17"/>
@@ -4399,6 +5358,9 @@
       <x:c r="H320" s="43" t="str">
         <x:f>IF(D320=40,200,IF(D320=30,150,""))</x:f>
       </x:c>
+      <x:c r="I320" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="17"/>
@@ -4411,6 +5373,9 @@
       <x:c r="H321" s="43" t="str">
         <x:f>IF(D321=40,200,IF(D321=30,150,""))</x:f>
       </x:c>
+      <x:c r="I321" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="17"/>
@@ -4423,6 +5388,9 @@
       <x:c r="H322" s="43" t="str">
         <x:f>IF(D322=40,200,IF(D322=30,150,""))</x:f>
       </x:c>
+      <x:c r="I322" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="17"/>
@@ -4435,6 +5403,9 @@
       <x:c r="H323" s="43" t="str">
         <x:f>IF(D323=40,200,IF(D323=30,150,""))</x:f>
       </x:c>
+      <x:c r="I323" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="17"/>
@@ -4447,6 +5418,9 @@
       <x:c r="H324" s="43" t="str">
         <x:f>IF(D324=40,200,IF(D324=30,150,""))</x:f>
       </x:c>
+      <x:c r="I324" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="17"/>
@@ -4459,6 +5433,9 @@
       <x:c r="H325" s="43" t="str">
         <x:f>IF(D325=40,200,IF(D325=30,150,""))</x:f>
       </x:c>
+      <x:c r="I325" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="17"/>
@@ -4471,6 +5448,9 @@
       <x:c r="H326" s="43" t="str">
         <x:f>IF(D326=40,200,IF(D326=30,150,""))</x:f>
       </x:c>
+      <x:c r="I326" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="17"/>
@@ -4483,6 +5463,9 @@
       <x:c r="H327" s="43" t="str">
         <x:f>IF(D327=40,200,IF(D327=30,150,""))</x:f>
       </x:c>
+      <x:c r="I327" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="17"/>
@@ -4495,6 +5478,9 @@
       <x:c r="H328" s="43" t="str">
         <x:f>IF(D328=40,200,IF(D328=30,150,""))</x:f>
       </x:c>
+      <x:c r="I328" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="17"/>
@@ -4507,6 +5493,9 @@
       <x:c r="H329" s="43" t="str">
         <x:f>IF(D329=40,200,IF(D329=30,150,""))</x:f>
       </x:c>
+      <x:c r="I329" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="17"/>
@@ -4519,6 +5508,9 @@
       <x:c r="H330" s="43" t="str">
         <x:f>IF(D330=40,200,IF(D330=30,150,""))</x:f>
       </x:c>
+      <x:c r="I330" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="17"/>
@@ -4531,6 +5523,9 @@
       <x:c r="H331" s="43" t="str">
         <x:f>IF(D331=40,200,IF(D331=30,150,""))</x:f>
       </x:c>
+      <x:c r="I331" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="17"/>
@@ -4543,6 +5538,9 @@
       <x:c r="H332" s="43" t="str">
         <x:f>IF(D332=40,200,IF(D332=30,150,""))</x:f>
       </x:c>
+      <x:c r="I332" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="17"/>
@@ -4555,6 +5553,9 @@
       <x:c r="H333" s="43" t="str">
         <x:f>IF(D333=40,200,IF(D333=30,150,""))</x:f>
       </x:c>
+      <x:c r="I333" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="17"/>
@@ -4567,6 +5568,9 @@
       <x:c r="H334" s="43" t="str">
         <x:f>IF(D334=40,200,IF(D334=30,150,""))</x:f>
       </x:c>
+      <x:c r="I334" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="17"/>
@@ -4579,6 +5583,9 @@
       <x:c r="H335" s="43" t="str">
         <x:f>IF(D335=40,200,IF(D335=30,150,""))</x:f>
       </x:c>
+      <x:c r="I335" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="17"/>
@@ -4591,6 +5598,9 @@
       <x:c r="H336" s="43" t="str">
         <x:f>IF(D336=40,200,IF(D336=30,150,""))</x:f>
       </x:c>
+      <x:c r="I336" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="17"/>
@@ -4603,6 +5613,9 @@
       <x:c r="H337" s="43" t="str">
         <x:f>IF(D337=40,200,IF(D337=30,150,""))</x:f>
       </x:c>
+      <x:c r="I337" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="17"/>
@@ -4615,6 +5628,9 @@
       <x:c r="H338" s="43" t="str">
         <x:f>IF(D338=40,200,IF(D338=30,150,""))</x:f>
       </x:c>
+      <x:c r="I338" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="17"/>
@@ -4627,6 +5643,9 @@
       <x:c r="H339" s="43" t="str">
         <x:f>IF(D339=40,200,IF(D339=30,150,""))</x:f>
       </x:c>
+      <x:c r="I339" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="17"/>
@@ -4639,6 +5658,9 @@
       <x:c r="H340" s="43" t="str">
         <x:f>IF(D340=40,200,IF(D340=30,150,""))</x:f>
       </x:c>
+      <x:c r="I340" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="17"/>
@@ -4651,6 +5673,9 @@
       <x:c r="H341" s="43" t="str">
         <x:f>IF(D341=40,200,IF(D341=30,150,""))</x:f>
       </x:c>
+      <x:c r="I341" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="17"/>
@@ -4663,6 +5688,9 @@
       <x:c r="H342" s="43" t="str">
         <x:f>IF(D342=40,200,IF(D342=30,150,""))</x:f>
       </x:c>
+      <x:c r="I342" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="17"/>
@@ -4675,6 +5703,9 @@
       <x:c r="H343" s="43" t="str">
         <x:f>IF(D343=40,200,IF(D343=30,150,""))</x:f>
       </x:c>
+      <x:c r="I343" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="17"/>
@@ -4687,6 +5718,9 @@
       <x:c r="H344" s="43" t="str">
         <x:f>IF(D344=40,200,IF(D344=30,150,""))</x:f>
       </x:c>
+      <x:c r="I344" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="17"/>
@@ -4699,6 +5733,9 @@
       <x:c r="H345" s="43" t="str">
         <x:f>IF(D345=40,200,IF(D345=30,150,""))</x:f>
       </x:c>
+      <x:c r="I345" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="17"/>
@@ -4711,6 +5748,9 @@
       <x:c r="H346" s="43" t="str">
         <x:f>IF(D346=40,200,IF(D346=30,150,""))</x:f>
       </x:c>
+      <x:c r="I346" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="17"/>
@@ -4723,6 +5763,9 @@
       <x:c r="H347" s="43" t="str">
         <x:f>IF(D347=40,200,IF(D347=30,150,""))</x:f>
       </x:c>
+      <x:c r="I347" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="17"/>
@@ -4735,6 +5778,9 @@
       <x:c r="H348" s="43" t="str">
         <x:f>IF(D348=40,200,IF(D348=30,150,""))</x:f>
       </x:c>
+      <x:c r="I348" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="17"/>
@@ -4747,6 +5793,9 @@
       <x:c r="H349" s="43" t="str">
         <x:f>IF(D349=40,200,IF(D349=30,150,""))</x:f>
       </x:c>
+      <x:c r="I349" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="17"/>
@@ -4759,6 +5808,9 @@
       <x:c r="H350" s="43" t="str">
         <x:f>IF(D350=40,200,IF(D350=30,150,""))</x:f>
       </x:c>
+      <x:c r="I350" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="17"/>
@@ -4771,6 +5823,9 @@
       <x:c r="H351" s="43" t="str">
         <x:f>IF(D351=40,200,IF(D351=30,150,""))</x:f>
       </x:c>
+      <x:c r="I351" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="17"/>
@@ -4783,6 +5838,9 @@
       <x:c r="H352" s="43" t="str">
         <x:f>IF(D352=40,200,IF(D352=30,150,""))</x:f>
       </x:c>
+      <x:c r="I352" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="17"/>
@@ -4795,6 +5853,9 @@
       <x:c r="H353" s="43" t="str">
         <x:f>IF(D353=40,200,IF(D353=30,150,""))</x:f>
       </x:c>
+      <x:c r="I353" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="17"/>
@@ -4807,6 +5868,9 @@
       <x:c r="H354" s="43" t="str">
         <x:f>IF(D354=40,200,IF(D354=30,150,""))</x:f>
       </x:c>
+      <x:c r="I354" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="17"/>
@@ -4819,6 +5883,9 @@
       <x:c r="H355" s="43" t="str">
         <x:f>IF(D355=40,200,IF(D355=30,150,""))</x:f>
       </x:c>
+      <x:c r="I355" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="17"/>
@@ -4831,6 +5898,9 @@
       <x:c r="H356" s="43" t="str">
         <x:f>IF(D356=40,200,IF(D356=30,150,""))</x:f>
       </x:c>
+      <x:c r="I356" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="17"/>
@@ -4843,6 +5913,9 @@
       <x:c r="H357" s="43" t="str">
         <x:f>IF(D357=40,200,IF(D357=30,150,""))</x:f>
       </x:c>
+      <x:c r="I357" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="17"/>
@@ -4855,6 +5928,9 @@
       <x:c r="H358" s="43" t="str">
         <x:f>IF(D358=40,200,IF(D358=30,150,""))</x:f>
       </x:c>
+      <x:c r="I358" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="17"/>
@@ -4867,6 +5943,9 @@
       <x:c r="H359" s="43" t="str">
         <x:f>IF(D359=40,200,IF(D359=30,150,""))</x:f>
       </x:c>
+      <x:c r="I359" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="17"/>
@@ -4879,6 +5958,9 @@
       <x:c r="H360" s="43" t="str">
         <x:f>IF(D360=40,200,IF(D360=30,150,""))</x:f>
       </x:c>
+      <x:c r="I360" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="17"/>
@@ -4891,6 +5973,9 @@
       <x:c r="H361" s="43" t="str">
         <x:f>IF(D361=40,200,IF(D361=30,150,""))</x:f>
       </x:c>
+      <x:c r="I361" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="17"/>
@@ -4903,6 +5988,9 @@
       <x:c r="H362" s="43" t="str">
         <x:f>IF(D362=40,200,IF(D362=30,150,""))</x:f>
       </x:c>
+      <x:c r="I362" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="17"/>
@@ -4915,6 +6003,9 @@
       <x:c r="H363" s="43" t="str">
         <x:f>IF(D363=40,200,IF(D363=30,150,""))</x:f>
       </x:c>
+      <x:c r="I363" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="17"/>
@@ -4927,6 +6018,9 @@
       <x:c r="H364" s="43" t="str">
         <x:f>IF(D364=40,200,IF(D364=30,150,""))</x:f>
       </x:c>
+      <x:c r="I364" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="17"/>
@@ -4939,6 +6033,9 @@
       <x:c r="H365" s="43" t="str">
         <x:f>IF(D365=40,200,IF(D365=30,150,""))</x:f>
       </x:c>
+      <x:c r="I365" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="17"/>
@@ -4951,6 +6048,9 @@
       <x:c r="H366" s="43" t="str">
         <x:f>IF(D366=40,200,IF(D366=30,150,""))</x:f>
       </x:c>
+      <x:c r="I366" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="17"/>
@@ -4963,6 +6063,9 @@
       <x:c r="H367" s="43" t="str">
         <x:f>IF(D367=40,200,IF(D367=30,150,""))</x:f>
       </x:c>
+      <x:c r="I367" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="17"/>
@@ -4975,6 +6078,9 @@
       <x:c r="H368" s="43" t="str">
         <x:f>IF(D368=40,200,IF(D368=30,150,""))</x:f>
       </x:c>
+      <x:c r="I368" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="17"/>
@@ -4987,6 +6093,9 @@
       <x:c r="H369" s="43" t="str">
         <x:f>IF(D369=40,200,IF(D369=30,150,""))</x:f>
       </x:c>
+      <x:c r="I369" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="17"/>
@@ -4999,6 +6108,9 @@
       <x:c r="H370" s="43" t="str">
         <x:f>IF(D370=40,200,IF(D370=30,150,""))</x:f>
       </x:c>
+      <x:c r="I370" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="17"/>
@@ -5011,6 +6123,9 @@
       <x:c r="H371" s="43" t="str">
         <x:f>IF(D371=40,200,IF(D371=30,150,""))</x:f>
       </x:c>
+      <x:c r="I371" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="17"/>
@@ -5023,6 +6138,9 @@
       <x:c r="H372" s="43" t="str">
         <x:f>IF(D372=40,200,IF(D372=30,150,""))</x:f>
       </x:c>
+      <x:c r="I372" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="17"/>
@@ -5035,6 +6153,9 @@
       <x:c r="H373" s="43" t="str">
         <x:f>IF(D373=40,200,IF(D373=30,150,""))</x:f>
       </x:c>
+      <x:c r="I373" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="17"/>
@@ -5047,6 +6168,9 @@
       <x:c r="H374" s="43" t="str">
         <x:f>IF(D374=40,200,IF(D374=30,150,""))</x:f>
       </x:c>
+      <x:c r="I374" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="17"/>
@@ -5059,6 +6183,9 @@
       <x:c r="H375" s="43" t="str">
         <x:f>IF(D375=40,200,IF(D375=30,150,""))</x:f>
       </x:c>
+      <x:c r="I375" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="17"/>
@@ -5071,6 +6198,9 @@
       <x:c r="H376" s="43" t="str">
         <x:f>IF(D376=40,200,IF(D376=30,150,""))</x:f>
       </x:c>
+      <x:c r="I376" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="17"/>
@@ -5083,6 +6213,9 @@
       <x:c r="H377" s="43" t="str">
         <x:f>IF(D377=40,200,IF(D377=30,150,""))</x:f>
       </x:c>
+      <x:c r="I377" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="17"/>
@@ -5095,6 +6228,9 @@
       <x:c r="H378" s="43" t="str">
         <x:f>IF(D378=40,200,IF(D378=30,150,""))</x:f>
       </x:c>
+      <x:c r="I378" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="17"/>
@@ -5107,6 +6243,9 @@
       <x:c r="H379" s="43" t="str">
         <x:f>IF(D379=40,200,IF(D379=30,150,""))</x:f>
       </x:c>
+      <x:c r="I379" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="17"/>
@@ -5119,6 +6258,9 @@
       <x:c r="H380" s="43" t="str">
         <x:f>IF(D380=40,200,IF(D380=30,150,""))</x:f>
       </x:c>
+      <x:c r="I380" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="17"/>
@@ -5131,6 +6273,9 @@
       <x:c r="H381" s="43" t="str">
         <x:f>IF(D381=40,200,IF(D381=30,150,""))</x:f>
       </x:c>
+      <x:c r="I381" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="17"/>
@@ -5143,6 +6288,9 @@
       <x:c r="H382" s="43" t="str">
         <x:f>IF(D382=40,200,IF(D382=30,150,""))</x:f>
       </x:c>
+      <x:c r="I382" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="17"/>
@@ -5155,6 +6303,9 @@
       <x:c r="H383" s="43" t="str">
         <x:f>IF(D383=40,200,IF(D383=30,150,""))</x:f>
       </x:c>
+      <x:c r="I383" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="17"/>
@@ -5167,6 +6318,9 @@
       <x:c r="H384" s="43" t="str">
         <x:f>IF(D384=40,200,IF(D384=30,150,""))</x:f>
       </x:c>
+      <x:c r="I384" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="17"/>
@@ -5179,6 +6333,9 @@
       <x:c r="H385" s="43" t="str">
         <x:f>IF(D385=40,200,IF(D385=30,150,""))</x:f>
       </x:c>
+      <x:c r="I385" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="17"/>
@@ -5191,6 +6348,9 @@
       <x:c r="H386" s="43" t="str">
         <x:f>IF(D386=40,200,IF(D386=30,150,""))</x:f>
       </x:c>
+      <x:c r="I386" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="17"/>
@@ -5203,6 +6363,9 @@
       <x:c r="H387" s="43" t="str">
         <x:f>IF(D387=40,200,IF(D387=30,150,""))</x:f>
       </x:c>
+      <x:c r="I387" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="17"/>
@@ -5215,6 +6378,9 @@
       <x:c r="H388" s="43" t="str">
         <x:f>IF(D388=40,200,IF(D388=30,150,""))</x:f>
       </x:c>
+      <x:c r="I388" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="17"/>
@@ -5227,6 +6393,9 @@
       <x:c r="H389" s="43" t="str">
         <x:f>IF(D389=40,200,IF(D389=30,150,""))</x:f>
       </x:c>
+      <x:c r="I389" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="17"/>
@@ -5239,6 +6408,9 @@
       <x:c r="H390" s="43" t="str">
         <x:f>IF(D390=40,200,IF(D390=30,150,""))</x:f>
       </x:c>
+      <x:c r="I390" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="17"/>
@@ -5251,6 +6423,9 @@
       <x:c r="H391" s="43" t="str">
         <x:f>IF(D391=40,200,IF(D391=30,150,""))</x:f>
       </x:c>
+      <x:c r="I391" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="17"/>
@@ -5263,6 +6438,9 @@
       <x:c r="H392" s="43" t="str">
         <x:f>IF(D392=40,200,IF(D392=30,150,""))</x:f>
       </x:c>
+      <x:c r="I392" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="17"/>
@@ -5275,6 +6453,9 @@
       <x:c r="H393" s="43" t="str">
         <x:f>IF(D393=40,200,IF(D393=30,150,""))</x:f>
       </x:c>
+      <x:c r="I393" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="17"/>
@@ -5287,6 +6468,9 @@
       <x:c r="H394" s="43" t="str">
         <x:f>IF(D394=40,200,IF(D394=30,150,""))</x:f>
       </x:c>
+      <x:c r="I394" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="17"/>
@@ -5299,6 +6483,9 @@
       <x:c r="H395" s="43" t="str">
         <x:f>IF(D395=40,200,IF(D395=30,150,""))</x:f>
       </x:c>
+      <x:c r="I395" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="17"/>
@@ -5311,6 +6498,9 @@
       <x:c r="H396" s="43" t="str">
         <x:f>IF(D396=40,200,IF(D396=30,150,""))</x:f>
       </x:c>
+      <x:c r="I396" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="17"/>
@@ -5323,6 +6513,9 @@
       <x:c r="H397" s="43" t="str">
         <x:f>IF(D397=40,200,IF(D397=30,150,""))</x:f>
       </x:c>
+      <x:c r="I397" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="17"/>
@@ -5335,6 +6528,9 @@
       <x:c r="H398" s="43" t="str">
         <x:f>IF(D398=40,200,IF(D398=30,150,""))</x:f>
       </x:c>
+      <x:c r="I398" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="17"/>
@@ -5347,6 +6543,9 @@
       <x:c r="H399" s="43" t="str">
         <x:f>IF(D399=40,200,IF(D399=30,150,""))</x:f>
       </x:c>
+      <x:c r="I399" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="17"/>
@@ -5359,6 +6558,9 @@
       <x:c r="H400" s="43" t="str">
         <x:f>IF(D400=40,200,IF(D400=30,150,""))</x:f>
       </x:c>
+      <x:c r="I400" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="17"/>
@@ -5371,6 +6573,9 @@
       <x:c r="H401" s="43" t="str">
         <x:f>IF(D401=40,200,IF(D401=30,150,""))</x:f>
       </x:c>
+      <x:c r="I401" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="17"/>
@@ -5383,6 +6588,9 @@
       <x:c r="H402" s="43" t="str">
         <x:f>IF(D402=40,200,IF(D402=30,150,""))</x:f>
       </x:c>
+      <x:c r="I402" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="17"/>
@@ -5395,6 +6603,9 @@
       <x:c r="H403" s="43" t="str">
         <x:f>IF(D403=40,200,IF(D403=30,150,""))</x:f>
       </x:c>
+      <x:c r="I403" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="17"/>
@@ -5407,6 +6618,9 @@
       <x:c r="H404" s="43" t="str">
         <x:f>IF(D404=40,200,IF(D404=30,150,""))</x:f>
       </x:c>
+      <x:c r="I404" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="17"/>
@@ -5419,6 +6633,9 @@
       <x:c r="H405" s="43" t="str">
         <x:f>IF(D405=40,200,IF(D405=30,150,""))</x:f>
       </x:c>
+      <x:c r="I405" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="17"/>
@@ -5431,6 +6648,9 @@
       <x:c r="H406" s="43" t="str">
         <x:f>IF(D406=40,200,IF(D406=30,150,""))</x:f>
       </x:c>
+      <x:c r="I406" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="17"/>
@@ -5443,6 +6663,9 @@
       <x:c r="H407" s="43" t="str">
         <x:f>IF(D407=40,200,IF(D407=30,150,""))</x:f>
       </x:c>
+      <x:c r="I407" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="17"/>
@@ -5455,6 +6678,9 @@
       <x:c r="H408" s="43" t="str">
         <x:f>IF(D408=40,200,IF(D408=30,150,""))</x:f>
       </x:c>
+      <x:c r="I408" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="17"/>
@@ -5467,6 +6693,9 @@
       <x:c r="H409" s="43" t="str">
         <x:f>IF(D409=40,200,IF(D409=30,150,""))</x:f>
       </x:c>
+      <x:c r="I409" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="17"/>
@@ -5479,6 +6708,9 @@
       <x:c r="H410" s="43" t="str">
         <x:f>IF(D410=40,200,IF(D410=30,150,""))</x:f>
       </x:c>
+      <x:c r="I410" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="17"/>
@@ -5491,6 +6723,9 @@
       <x:c r="H411" s="43" t="str">
         <x:f>IF(D411=40,200,IF(D411=30,150,""))</x:f>
       </x:c>
+      <x:c r="I411" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="412">
       <x:c r="A412" s="17"/>
@@ -5503,6 +6738,9 @@
       <x:c r="H412" s="43" t="str">
         <x:f>IF(D412=40,200,IF(D412=30,150,""))</x:f>
       </x:c>
+      <x:c r="I412" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="413">
       <x:c r="A413" s="17"/>
@@ -5515,6 +6753,9 @@
       <x:c r="H413" s="43" t="str">
         <x:f>IF(D413=40,200,IF(D413=30,150,""))</x:f>
       </x:c>
+      <x:c r="I413" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="414">
       <x:c r="A414" s="17"/>
@@ -5527,6 +6768,9 @@
       <x:c r="H414" s="43" t="str">
         <x:f>IF(D414=40,200,IF(D414=30,150,""))</x:f>
       </x:c>
+      <x:c r="I414" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="17"/>
@@ -5539,6 +6783,9 @@
       <x:c r="H415" s="43" t="str">
         <x:f>IF(D415=40,200,IF(D415=30,150,""))</x:f>
       </x:c>
+      <x:c r="I415" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="17"/>
@@ -5551,6 +6798,9 @@
       <x:c r="H416" s="43" t="str">
         <x:f>IF(D416=40,200,IF(D416=30,150,""))</x:f>
       </x:c>
+      <x:c r="I416" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="417">
       <x:c r="A417" s="17"/>
@@ -5563,6 +6813,9 @@
       <x:c r="H417" s="43" t="str">
         <x:f>IF(D417=40,200,IF(D417=30,150,""))</x:f>
       </x:c>
+      <x:c r="I417" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="418">
       <x:c r="A418" s="17"/>
@@ -5575,6 +6828,9 @@
       <x:c r="H418" s="43" t="str">
         <x:f>IF(D418=40,200,IF(D418=30,150,""))</x:f>
       </x:c>
+      <x:c r="I418" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="419">
       <x:c r="A419" s="17"/>
@@ -5587,6 +6843,9 @@
       <x:c r="H419" s="43" t="str">
         <x:f>IF(D419=40,200,IF(D419=30,150,""))</x:f>
       </x:c>
+      <x:c r="I419" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="17"/>
@@ -5599,6 +6858,9 @@
       <x:c r="H420" s="43" t="str">
         <x:f>IF(D420=40,200,IF(D420=30,150,""))</x:f>
       </x:c>
+      <x:c r="I420" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="421">
       <x:c r="A421" s="17"/>
@@ -5611,6 +6873,9 @@
       <x:c r="H421" s="43" t="str">
         <x:f>IF(D421=40,200,IF(D421=30,150,""))</x:f>
       </x:c>
+      <x:c r="I421" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="422">
       <x:c r="A422" s="17"/>
@@ -5623,6 +6888,9 @@
       <x:c r="H422" s="43" t="str">
         <x:f>IF(D422=40,200,IF(D422=30,150,""))</x:f>
       </x:c>
+      <x:c r="I422" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="423">
       <x:c r="A423" s="17"/>
@@ -5635,6 +6903,9 @@
       <x:c r="H423" s="43" t="str">
         <x:f>IF(D423=40,200,IF(D423=30,150,""))</x:f>
       </x:c>
+      <x:c r="I423" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="424">
       <x:c r="A424" s="17"/>
@@ -5647,6 +6918,9 @@
       <x:c r="H424" s="43" t="str">
         <x:f>IF(D424=40,200,IF(D424=30,150,""))</x:f>
       </x:c>
+      <x:c r="I424" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="17"/>
@@ -5659,6 +6933,9 @@
       <x:c r="H425" s="43" t="str">
         <x:f>IF(D425=40,200,IF(D425=30,150,""))</x:f>
       </x:c>
+      <x:c r="I425" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="17"/>
@@ -5671,6 +6948,9 @@
       <x:c r="H426" s="43" t="str">
         <x:f>IF(D426=40,200,IF(D426=30,150,""))</x:f>
       </x:c>
+      <x:c r="I426" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="427">
       <x:c r="A427" s="17"/>
@@ -5683,6 +6963,9 @@
       <x:c r="H427" s="43" t="str">
         <x:f>IF(D427=40,200,IF(D427=30,150,""))</x:f>
       </x:c>
+      <x:c r="I427" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="428">
       <x:c r="A428" s="17"/>
@@ -5695,6 +6978,9 @@
       <x:c r="H428" s="43" t="str">
         <x:f>IF(D428=40,200,IF(D428=30,150,""))</x:f>
       </x:c>
+      <x:c r="I428" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="17"/>
@@ -5707,6 +6993,9 @@
       <x:c r="H429" s="43" t="str">
         <x:f>IF(D429=40,200,IF(D429=30,150,""))</x:f>
       </x:c>
+      <x:c r="I429" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="430">
       <x:c r="A430" s="17"/>
@@ -5719,6 +7008,9 @@
       <x:c r="H430" s="43" t="str">
         <x:f>IF(D430=40,200,IF(D430=30,150,""))</x:f>
       </x:c>
+      <x:c r="I430" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="17"/>
@@ -5731,6 +7023,9 @@
       <x:c r="H431" s="43" t="str">
         <x:f>IF(D431=40,200,IF(D431=30,150,""))</x:f>
       </x:c>
+      <x:c r="I431" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="432">
       <x:c r="A432" s="17"/>
@@ -5743,6 +7038,9 @@
       <x:c r="H432" s="43" t="str">
         <x:f>IF(D432=40,200,IF(D432=30,150,""))</x:f>
       </x:c>
+      <x:c r="I432" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="17"/>
@@ -5755,6 +7053,9 @@
       <x:c r="H433" s="43" t="str">
         <x:f>IF(D433=40,200,IF(D433=30,150,""))</x:f>
       </x:c>
+      <x:c r="I433" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="434">
       <x:c r="A434" s="17"/>
@@ -5767,6 +7068,9 @@
       <x:c r="H434" s="43" t="str">
         <x:f>IF(D434=40,200,IF(D434=30,150,""))</x:f>
       </x:c>
+      <x:c r="I434" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="17"/>
@@ -5779,6 +7083,9 @@
       <x:c r="H435" s="43" t="str">
         <x:f>IF(D435=40,200,IF(D435=30,150,""))</x:f>
       </x:c>
+      <x:c r="I435" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="17"/>
@@ -5791,6 +7098,9 @@
       <x:c r="H436" s="43" t="str">
         <x:f>IF(D436=40,200,IF(D436=30,150,""))</x:f>
       </x:c>
+      <x:c r="I436" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="17"/>
@@ -5803,6 +7113,9 @@
       <x:c r="H437" s="43" t="str">
         <x:f>IF(D437=40,200,IF(D437=30,150,""))</x:f>
       </x:c>
+      <x:c r="I437" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="438">
       <x:c r="A438" s="17"/>
@@ -5815,6 +7128,9 @@
       <x:c r="H438" s="43" t="str">
         <x:f>IF(D438=40,200,IF(D438=30,150,""))</x:f>
       </x:c>
+      <x:c r="I438" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="17"/>
@@ -5827,6 +7143,9 @@
       <x:c r="H439" s="43" t="str">
         <x:f>IF(D439=40,200,IF(D439=30,150,""))</x:f>
       </x:c>
+      <x:c r="I439" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="17"/>
@@ -5839,6 +7158,9 @@
       <x:c r="H440" s="43" t="str">
         <x:f>IF(D440=40,200,IF(D440=30,150,""))</x:f>
       </x:c>
+      <x:c r="I440" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="17"/>
@@ -5851,6 +7173,9 @@
       <x:c r="H441" s="43" t="str">
         <x:f>IF(D441=40,200,IF(D441=30,150,""))</x:f>
       </x:c>
+      <x:c r="I441" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="442">
       <x:c r="A442" s="17"/>
@@ -5863,6 +7188,9 @@
       <x:c r="H442" s="43" t="str">
         <x:f>IF(D442=40,200,IF(D442=30,150,""))</x:f>
       </x:c>
+      <x:c r="I442" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="443">
       <x:c r="A443" s="17"/>
@@ -5875,6 +7203,9 @@
       <x:c r="H443" s="43" t="str">
         <x:f>IF(D443=40,200,IF(D443=30,150,""))</x:f>
       </x:c>
+      <x:c r="I443" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="444">
       <x:c r="A444" s="17"/>
@@ -5887,6 +7218,9 @@
       <x:c r="H444" s="43" t="str">
         <x:f>IF(D444=40,200,IF(D444=30,150,""))</x:f>
       </x:c>
+      <x:c r="I444" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="17"/>
@@ -5899,6 +7233,9 @@
       <x:c r="H445" s="43" t="str">
         <x:f>IF(D445=40,200,IF(D445=30,150,""))</x:f>
       </x:c>
+      <x:c r="I445" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="17"/>
@@ -5911,6 +7248,9 @@
       <x:c r="H446" s="43" t="str">
         <x:f>IF(D446=40,200,IF(D446=30,150,""))</x:f>
       </x:c>
+      <x:c r="I446" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="447">
       <x:c r="A447" s="17"/>
@@ -5923,6 +7263,9 @@
       <x:c r="H447" s="43" t="str">
         <x:f>IF(D447=40,200,IF(D447=30,150,""))</x:f>
       </x:c>
+      <x:c r="I447" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="448">
       <x:c r="A448" s="17"/>
@@ -5935,6 +7278,9 @@
       <x:c r="H448" s="43" t="str">
         <x:f>IF(D448=40,200,IF(D448=30,150,""))</x:f>
       </x:c>
+      <x:c r="I448" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="17"/>
@@ -5947,6 +7293,9 @@
       <x:c r="H449" s="43" t="str">
         <x:f>IF(D449=40,200,IF(D449=30,150,""))</x:f>
       </x:c>
+      <x:c r="I449" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="17"/>
@@ -5959,6 +7308,9 @@
       <x:c r="H450" s="43" t="str">
         <x:f>IF(D450=40,200,IF(D450=30,150,""))</x:f>
       </x:c>
+      <x:c r="I450" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="17"/>
@@ -5971,6 +7323,9 @@
       <x:c r="H451" s="43" t="str">
         <x:f>IF(D451=40,200,IF(D451=30,150,""))</x:f>
       </x:c>
+      <x:c r="I451" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="452">
       <x:c r="A452" s="17"/>
@@ -5983,6 +7338,9 @@
       <x:c r="H452" s="43" t="str">
         <x:f>IF(D452=40,200,IF(D452=30,150,""))</x:f>
       </x:c>
+      <x:c r="I452" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="17"/>
@@ -5995,6 +7353,9 @@
       <x:c r="H453" s="43" t="str">
         <x:f>IF(D453=40,200,IF(D453=30,150,""))</x:f>
       </x:c>
+      <x:c r="I453" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="17"/>
@@ -6007,6 +7368,9 @@
       <x:c r="H454" s="43" t="str">
         <x:f>IF(D454=40,200,IF(D454=30,150,""))</x:f>
       </x:c>
+      <x:c r="I454" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="455">
       <x:c r="A455" s="17"/>
@@ -6019,6 +7383,9 @@
       <x:c r="H455" s="43" t="str">
         <x:f>IF(D455=40,200,IF(D455=30,150,""))</x:f>
       </x:c>
+      <x:c r="I455" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="17"/>
@@ -6031,6 +7398,9 @@
       <x:c r="H456" s="43" t="str">
         <x:f>IF(D456=40,200,IF(D456=30,150,""))</x:f>
       </x:c>
+      <x:c r="I456" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="457">
       <x:c r="A457" s="17"/>
@@ -6043,6 +7413,9 @@
       <x:c r="H457" s="43" t="str">
         <x:f>IF(D457=40,200,IF(D457=30,150,""))</x:f>
       </x:c>
+      <x:c r="I457" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="458">
       <x:c r="A458" s="17"/>
@@ -6055,6 +7428,9 @@
       <x:c r="H458" s="43" t="str">
         <x:f>IF(D458=40,200,IF(D458=30,150,""))</x:f>
       </x:c>
+      <x:c r="I458" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="459">
       <x:c r="A459" s="17"/>
@@ -6067,6 +7443,9 @@
       <x:c r="H459" s="43" t="str">
         <x:f>IF(D459=40,200,IF(D459=30,150,""))</x:f>
       </x:c>
+      <x:c r="I459" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="17"/>
@@ -6079,6 +7458,9 @@
       <x:c r="H460" s="43" t="str">
         <x:f>IF(D460=40,200,IF(D460=30,150,""))</x:f>
       </x:c>
+      <x:c r="I460" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="461">
       <x:c r="A461" s="17"/>
@@ -6091,6 +7473,9 @@
       <x:c r="H461" s="43" t="str">
         <x:f>IF(D461=40,200,IF(D461=30,150,""))</x:f>
       </x:c>
+      <x:c r="I461" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="462">
       <x:c r="A462" s="17"/>
@@ -6103,6 +7488,9 @@
       <x:c r="H462" s="43" t="str">
         <x:f>IF(D462=40,200,IF(D462=30,150,""))</x:f>
       </x:c>
+      <x:c r="I462" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="463">
       <x:c r="A463" s="17"/>
@@ -6115,6 +7503,9 @@
       <x:c r="H463" s="43" t="str">
         <x:f>IF(D463=40,200,IF(D463=30,150,""))</x:f>
       </x:c>
+      <x:c r="I463" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="464">
       <x:c r="A464" s="17"/>
@@ -6127,6 +7518,9 @@
       <x:c r="H464" s="43" t="str">
         <x:f>IF(D464=40,200,IF(D464=30,150,""))</x:f>
       </x:c>
+      <x:c r="I464" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="465">
       <x:c r="A465" s="17"/>
@@ -6139,6 +7533,9 @@
       <x:c r="H465" s="43" t="str">
         <x:f>IF(D465=40,200,IF(D465=30,150,""))</x:f>
       </x:c>
+      <x:c r="I465" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="17"/>
@@ -6151,6 +7548,9 @@
       <x:c r="H466" s="43" t="str">
         <x:f>IF(D466=40,200,IF(D466=30,150,""))</x:f>
       </x:c>
+      <x:c r="I466" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="467">
       <x:c r="A467" s="17"/>
@@ -6163,6 +7563,9 @@
       <x:c r="H467" s="43" t="str">
         <x:f>IF(D467=40,200,IF(D467=30,150,""))</x:f>
       </x:c>
+      <x:c r="I467" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="468">
       <x:c r="A468" s="17"/>
@@ -6175,6 +7578,9 @@
       <x:c r="H468" s="43" t="str">
         <x:f>IF(D468=40,200,IF(D468=30,150,""))</x:f>
       </x:c>
+      <x:c r="I468" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="469">
       <x:c r="A469" s="17"/>
@@ -6187,6 +7593,9 @@
       <x:c r="H469" s="43" t="str">
         <x:f>IF(D469=40,200,IF(D469=30,150,""))</x:f>
       </x:c>
+      <x:c r="I469" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="470">
       <x:c r="A470" s="17"/>
@@ -6199,6 +7608,9 @@
       <x:c r="H470" s="43" t="str">
         <x:f>IF(D470=40,200,IF(D470=30,150,""))</x:f>
       </x:c>
+      <x:c r="I470" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="471">
       <x:c r="A471" s="17"/>
@@ -6211,6 +7623,9 @@
       <x:c r="H471" s="43" t="str">
         <x:f>IF(D471=40,200,IF(D471=30,150,""))</x:f>
       </x:c>
+      <x:c r="I471" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="472">
       <x:c r="A472" s="17"/>
@@ -6223,6 +7638,9 @@
       <x:c r="H472" s="43" t="str">
         <x:f>IF(D472=40,200,IF(D472=30,150,""))</x:f>
       </x:c>
+      <x:c r="I472" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="17"/>
@@ -6235,6 +7653,9 @@
       <x:c r="H473" s="43" t="str">
         <x:f>IF(D473=40,200,IF(D473=30,150,""))</x:f>
       </x:c>
+      <x:c r="I473" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="17"/>
@@ -6247,6 +7668,9 @@
       <x:c r="H474" s="43" t="str">
         <x:f>IF(D474=40,200,IF(D474=30,150,""))</x:f>
       </x:c>
+      <x:c r="I474" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="475">
       <x:c r="A475" s="17"/>
@@ -6259,6 +7683,9 @@
       <x:c r="H475" s="43" t="str">
         <x:f>IF(D475=40,200,IF(D475=30,150,""))</x:f>
       </x:c>
+      <x:c r="I475" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="476">
       <x:c r="A476" s="17"/>
@@ -6271,6 +7698,9 @@
       <x:c r="H476" s="43" t="str">
         <x:f>IF(D476=40,200,IF(D476=30,150,""))</x:f>
       </x:c>
+      <x:c r="I476" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="477">
       <x:c r="A477" s="17"/>
@@ -6283,6 +7713,9 @@
       <x:c r="H477" s="43" t="str">
         <x:f>IF(D477=40,200,IF(D477=30,150,""))</x:f>
       </x:c>
+      <x:c r="I477" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="478">
       <x:c r="A478" s="17"/>
@@ -6295,6 +7728,9 @@
       <x:c r="H478" s="43" t="str">
         <x:f>IF(D478=40,200,IF(D478=30,150,""))</x:f>
       </x:c>
+      <x:c r="I478" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="479">
       <x:c r="A479" s="17"/>
@@ -6307,6 +7743,9 @@
       <x:c r="H479" s="43" t="str">
         <x:f>IF(D479=40,200,IF(D479=30,150,""))</x:f>
       </x:c>
+      <x:c r="I479" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="17"/>
@@ -6319,6 +7758,9 @@
       <x:c r="H480" s="43" t="str">
         <x:f>IF(D480=40,200,IF(D480=30,150,""))</x:f>
       </x:c>
+      <x:c r="I480" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="481">
       <x:c r="A481" s="17"/>
@@ -6331,6 +7773,9 @@
       <x:c r="H481" s="43" t="str">
         <x:f>IF(D481=40,200,IF(D481=30,150,""))</x:f>
       </x:c>
+      <x:c r="I481" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="482">
       <x:c r="A482" s="17"/>
@@ -6343,6 +7788,9 @@
       <x:c r="H482" s="43" t="str">
         <x:f>IF(D482=40,200,IF(D482=30,150,""))</x:f>
       </x:c>
+      <x:c r="I482" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="483">
       <x:c r="A483" s="17"/>
@@ -6355,6 +7803,9 @@
       <x:c r="H483" s="43" t="str">
         <x:f>IF(D483=40,200,IF(D483=30,150,""))</x:f>
       </x:c>
+      <x:c r="I483" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="484">
       <x:c r="A484" s="17"/>
@@ -6367,6 +7818,9 @@
       <x:c r="H484" s="43" t="str">
         <x:f>IF(D484=40,200,IF(D484=30,150,""))</x:f>
       </x:c>
+      <x:c r="I484" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="485">
       <x:c r="A485" s="17"/>
@@ -6379,6 +7833,9 @@
       <x:c r="H485" s="43" t="str">
         <x:f>IF(D485=40,200,IF(D485=30,150,""))</x:f>
       </x:c>
+      <x:c r="I485" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="486">
       <x:c r="A486" s="17"/>
@@ -6391,6 +7848,9 @@
       <x:c r="H486" s="43" t="str">
         <x:f>IF(D486=40,200,IF(D486=30,150,""))</x:f>
       </x:c>
+      <x:c r="I486" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="487">
       <x:c r="A487" s="17"/>
@@ -6403,6 +7863,9 @@
       <x:c r="H487" s="43" t="str">
         <x:f>IF(D487=40,200,IF(D487=30,150,""))</x:f>
       </x:c>
+      <x:c r="I487" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="488">
       <x:c r="A488" s="17"/>
@@ -6415,6 +7878,9 @@
       <x:c r="H488" s="43" t="str">
         <x:f>IF(D488=40,200,IF(D488=30,150,""))</x:f>
       </x:c>
+      <x:c r="I488" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="489">
       <x:c r="A489" s="17"/>
@@ -6427,6 +7893,9 @@
       <x:c r="H489" s="43" t="str">
         <x:f>IF(D489=40,200,IF(D489=30,150,""))</x:f>
       </x:c>
+      <x:c r="I489" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="490">
       <x:c r="A490" s="17"/>
@@ -6439,6 +7908,9 @@
       <x:c r="H490" s="43" t="str">
         <x:f>IF(D490=40,200,IF(D490=30,150,""))</x:f>
       </x:c>
+      <x:c r="I490" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="491">
       <x:c r="A491" s="17"/>
@@ -6451,6 +7923,9 @@
       <x:c r="H491" s="43" t="str">
         <x:f>IF(D491=40,200,IF(D491=30,150,""))</x:f>
       </x:c>
+      <x:c r="I491" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="492">
       <x:c r="A492" s="17"/>
@@ -6463,6 +7938,9 @@
       <x:c r="H492" s="43" t="str">
         <x:f>IF(D492=40,200,IF(D492=30,150,""))</x:f>
       </x:c>
+      <x:c r="I492" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="493">
       <x:c r="A493" s="17"/>
@@ -6475,6 +7953,9 @@
       <x:c r="H493" s="43" t="str">
         <x:f>IF(D493=40,200,IF(D493=30,150,""))</x:f>
       </x:c>
+      <x:c r="I493" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="494">
       <x:c r="A494" s="17"/>
@@ -6487,6 +7968,9 @@
       <x:c r="H494" s="43" t="str">
         <x:f>IF(D494=40,200,IF(D494=30,150,""))</x:f>
       </x:c>
+      <x:c r="I494" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="495">
       <x:c r="A495" s="17"/>
@@ -6499,6 +7983,9 @@
       <x:c r="H495" s="43" t="str">
         <x:f>IF(D495=40,200,IF(D495=30,150,""))</x:f>
       </x:c>
+      <x:c r="I495" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="496">
       <x:c r="A496" s="17"/>
@@ -6511,6 +7998,9 @@
       <x:c r="H496" s="43" t="str">
         <x:f>IF(D496=40,200,IF(D496=30,150,""))</x:f>
       </x:c>
+      <x:c r="I496" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="497">
       <x:c r="A497" s="17"/>
@@ -6523,6 +8013,9 @@
       <x:c r="H497" s="43" t="str">
         <x:f>IF(D497=40,200,IF(D497=30,150,""))</x:f>
       </x:c>
+      <x:c r="I497" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="498">
       <x:c r="A498" s="17"/>
@@ -6535,6 +8028,9 @@
       <x:c r="H498" s="43" t="str">
         <x:f>IF(D498=40,200,IF(D498=30,150,""))</x:f>
       </x:c>
+      <x:c r="I498" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="499">
       <x:c r="A499" s="17"/>
@@ -6547,6 +8043,9 @@
       <x:c r="H499" s="43" t="str">
         <x:f>IF(D499=40,200,IF(D499=30,150,""))</x:f>
       </x:c>
+      <x:c r="I499" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="500">
       <x:c r="A500" s="19"/>
@@ -6559,9 +8058,12 @@
       <x:c r="H500" s="44" t="str">
         <x:f>IF(D500=40,200,IF(D500=30,150,""))</x:f>
       </x:c>
+      <x:c r="I500" s="59" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="5">
+  <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="B2:B500">
       <x:formula1>Listas!$A$2:$A$8</x:formula1>
     </x:dataValidation>
@@ -6576,6 +8078,9 @@
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F2:F500">
       <x:formula1>Listas!$E$2:$E$3</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>Listas!$F$2:$F$3</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6639,7 +8144,7 @@
     </x:row>
     <x:row r="6" ht="29" customHeight="1">
       <x:c r="A6" s="63" t="str">
-        <x:v>3. Servidor de 40h: 200h mensais e turnos Matutino e Vespertino.</x:v>
+        <x:v>3. Servidor de 40h: o sistema considera 200h mensais e os turnos Matutino e Vespertino.</x:v>
       </x:c>
       <x:c r="B6" s="63"/>
       <x:c r="C6" s="63"/>
@@ -6651,7 +8156,7 @@
     </x:row>
     <x:row r="7" ht="29" customHeight="1">
       <x:c r="A7" s="63" t="str">
-        <x:v>4. Servidor de 30h: 150h mensais; escolha MATUTINO ou VESPERTINO.</x:v>
+        <x:v>4. Servidor de 30h: o sistema considera 150h mensais; escolha MATUTINO ou VESPERTINO.</x:v>
       </x:c>
       <x:c r="B7" s="63"/>
       <x:c r="C7" s="63"/>
@@ -6684,6 +8189,16 @@
       <x:c r="F9" s="63"/>
       <x:c r="G9" s="63"/>
       <x:c r="H9" s="63"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="59" t="str">
+        <x:v>7. Na coluna Lei Larissa, selecione Sim apenas para os servidores beneficiários.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="59" t="str">
+        <x:v>8. Por padrão, todos os servidores estão preenchidos como Não.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -6727,6 +8242,9 @@
       <x:c r="E1" s="3" t="str">
         <x:v>Coordenação</x:v>
       </x:c>
+      <x:c r="F1" t="str">
+        <x:v>Lei Larissa</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -6744,6 +8262,9 @@
       <x:c r="E2" t="str">
         <x:v>M</x:v>
       </x:c>
+      <x:c r="F2" t="str">
+        <x:v>Não</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -6760,6 +8281,9 @@
       </x:c>
       <x:c r="E3" t="str">
         <x:v>V</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Sim</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
